--- a/templates/KB_Market_Improvement_XLSForm_GT_HORECA.xlsx
+++ b/templates/KB_Market_Improvement_XLSForm_GT_HORECA.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R7e7755dd007140cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rd30bda7fd4154487"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R194b2f53e2f4474e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bot_Logic" sheetId="4" r:id="R934bd39a8c6a42cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bot_Data_Map" sheetId="5" r:id="Rb28efd42d3ec41f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R310741764b274695"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R322ac08f1d6747bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Recf18bacdeaa48e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bot_Logic" sheetId="4" r:id="Rf588a95fbaf84e92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bot_Data_Map" sheetId="5" r:id="R78f634dd91d6479d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1466,60 +1466,33 @@
     <x:t xml:space="preserve">fresh_wurkz_group</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">WURKZ</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">fresh_status_wurkz</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">WURKZ - ស្ថានភាពលក់</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">fresh_movement_score_wurkz</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">WURKZ - Movement Score 0-10</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">${fresh_status_wurkz} = 'sale' or ${fresh_status_wurkz} = 'fast_sale'</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">fresh_stock_status_wurkz</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">WURKZ - Stock Status</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">fresh_bbe_wurkz</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">WURKZ - BBE / Freshness Date</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">fresh_buy_in_price_wurkz</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">WURKZ - Buy In Price</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">fresh_sell_out_price_wurkz</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">WURKZ - Sell Out Price</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">fresh_new_purchase_wurkz</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">WURKZ - New Outlet Purchase</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">fresh_volume_wurkz</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">WURKZ - Volume (ctn)</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">comp_boostrong_group</x:t>
   </x:si>
   <x:si>
@@ -1748,40 +1721,22 @@
     <x:t xml:space="preserve">comp_dragon_group</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Dragon</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">comp_status_dragon</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Dragon - ស្ថានភាពលក់</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">comp_movement_score_dragon</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Dragon - Movement Score 0-10</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">${comp_status_dragon} = 'sale' or ${comp_status_dragon} = 'fast_sale'</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">comp_stock_status_dragon</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Dragon - Stock Status</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">comp_buy_in_price_dragon</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Dragon - Buy In Price</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">comp_sell_out_price_dragon</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dragon - Sell Out Price</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">fresh_dazz_zero_sugar_group</x:t>
@@ -9827,8 +9782,8 @@
       <x:c r="B226" s="1" t="s">
         <x:v>483</x:v>
       </x:c>
-      <x:c r="C226" s="1" t="s">
-        <x:v>484</x:v>
+      <x:c r="C226" s="1" t="str">
+        <x:v>WURKZ ORD</x:v>
       </x:c>
       <x:c r="D226" s="1" t="s">
         <x:v>14</x:v>
@@ -9850,10 +9805,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B227" s="1" t="s">
-        <x:v>485</x:v>
-      </x:c>
-      <x:c r="C227" s="1" t="s">
-        <x:v>486</x:v>
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="C227" s="1" t="str">
+        <x:v>WURKZ ORD - ស្ថានភាពលក់</x:v>
       </x:c>
       <x:c r="D227" s="1" t="s">
         <x:v>14</x:v>
@@ -9875,10 +9830,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B228" s="1" t="s">
-        <x:v>487</x:v>
-      </x:c>
-      <x:c r="C228" s="1" t="s">
-        <x:v>488</x:v>
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="C228" s="1" t="str">
+        <x:v>WURKZ ORD - Movement Score 0-10</x:v>
       </x:c>
       <x:c r="D228" s="1" t="s">
         <x:v>14</x:v>
@@ -9889,7 +9844,7 @@
       <x:c r="F228" s="1"/>
       <x:c r="G228" s="1"/>
       <x:c r="H228" s="1" t="s">
-        <x:v>489</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="I228" s="1" t="s">
         <x:v>102</x:v>
@@ -9904,10 +9859,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B229" s="1" t="s">
-        <x:v>490</x:v>
-      </x:c>
-      <x:c r="C229" s="1" t="s">
-        <x:v>491</x:v>
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="C229" s="1" t="str">
+        <x:v>WURKZ ORD - Stock Status</x:v>
       </x:c>
       <x:c r="D229" s="1" t="s">
         <x:v>14</x:v>
@@ -9931,10 +9886,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B230" s="1" t="s">
-        <x:v>492</x:v>
-      </x:c>
-      <x:c r="C230" s="1" t="s">
-        <x:v>493</x:v>
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="C230" s="1" t="str">
+        <x:v>WURKZ ORD - BBE / Freshness Date</x:v>
       </x:c>
       <x:c r="D230" s="1" t="s">
         <x:v>14</x:v>
@@ -9956,10 +9911,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B231" s="1" t="s">
-        <x:v>494</x:v>
-      </x:c>
-      <x:c r="C231" s="1" t="s">
-        <x:v>495</x:v>
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="C231" s="1" t="str">
+        <x:v>WURKZ ORD - Buy In Price</x:v>
       </x:c>
       <x:c r="D231" s="1" t="s">
         <x:v>14</x:v>
@@ -9985,10 +9940,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B232" s="1" t="s">
-        <x:v>496</x:v>
-      </x:c>
-      <x:c r="C232" s="1" t="s">
-        <x:v>497</x:v>
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="C232" s="1" t="str">
+        <x:v>WURKZ ORD - Sell Out Price</x:v>
       </x:c>
       <x:c r="D232" s="1" t="s">
         <x:v>14</x:v>
@@ -10014,10 +9969,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B233" s="1" t="s">
-        <x:v>498</x:v>
-      </x:c>
-      <x:c r="C233" s="1" t="s">
-        <x:v>499</x:v>
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="C233" s="1" t="str">
+        <x:v>WURKZ ORD - New Outlet Purchase</x:v>
       </x:c>
       <x:c r="D233" s="1" t="s">
         <x:v>14</x:v>
@@ -10041,10 +9996,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B234" s="1" t="s">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="C234" s="1" t="s">
-        <x:v>501</x:v>
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="C234" s="1" t="str">
+        <x:v>WURKZ ORD - Volume (ctn)</x:v>
       </x:c>
       <x:c r="D234" s="1" t="s">
         <x:v>14</x:v>
@@ -10087,7 +10042,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B236" s="1" t="s">
-        <x:v>502</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="C236" s="1" t="str">
         <x:v>Boostrong ORD</x:v>
@@ -10112,7 +10067,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B237" s="1" t="s">
-        <x:v>503</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="C237" s="1" t="str">
         <x:v>Boostrong ORD - ស្ថានភាពលក់</x:v>
@@ -10137,7 +10092,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B238" s="1" t="s">
-        <x:v>504</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="C238" s="1" t="str">
         <x:v>Boostrong ORD - Movement Score 0-10</x:v>
@@ -10151,7 +10106,7 @@
       <x:c r="F238" s="1"/>
       <x:c r="G238" s="1"/>
       <x:c r="H238" s="1" t="s">
-        <x:v>505</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="I238" s="1" t="s">
         <x:v>102</x:v>
@@ -10166,7 +10121,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B239" s="1" t="s">
-        <x:v>506</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="C239" s="1" t="str">
         <x:v>Boostrong ORD - Stock Status</x:v>
@@ -10193,7 +10148,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B240" s="1" t="s">
-        <x:v>507</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="C240" s="1" t="str">
         <x:v>Boostrong ORD - Buy In Price</x:v>
@@ -10222,7 +10177,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B241" s="1" t="s">
-        <x:v>508</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="C241" s="1" t="str">
         <x:v>Boostrong ORD - Sell Out Price</x:v>
@@ -10268,7 +10223,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B243" s="1" t="s">
-        <x:v>509</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="C243" s="1" t="str">
         <x:v>Krud ED ORD</x:v>
@@ -10293,7 +10248,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B244" s="1" t="s">
-        <x:v>510</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="C244" s="1" t="str">
         <x:v>Krud ED ORD - ស្ថានភាពលក់</x:v>
@@ -10318,7 +10273,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B245" s="1" t="s">
-        <x:v>511</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="C245" s="1" t="str">
         <x:v>Krud ED ORD - Movement Score 0-10</x:v>
@@ -10332,7 +10287,7 @@
       <x:c r="F245" s="1"/>
       <x:c r="G245" s="1"/>
       <x:c r="H245" s="1" t="s">
-        <x:v>512</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="I245" s="1" t="s">
         <x:v>102</x:v>
@@ -10347,7 +10302,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B246" s="1" t="s">
-        <x:v>513</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="C246" s="1" t="str">
         <x:v>Krud ED ORD - Stock Status</x:v>
@@ -10374,7 +10329,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B247" s="1" t="s">
-        <x:v>514</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="C247" s="1" t="str">
         <x:v>Krud ED ORD - Buy In Price</x:v>
@@ -10403,7 +10358,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B248" s="1" t="s">
-        <x:v>515</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="C248" s="1" t="str">
         <x:v>Krud ED ORD - Sell Out Price</x:v>
@@ -10449,7 +10404,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B250" s="1" t="s">
-        <x:v>516</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="C250" s="1" t="str">
         <x:v>CAMBODIA ED ORD</x:v>
@@ -10463,7 +10418,7 @@
       </x:c>
       <x:c r="G250" s="1"/>
       <x:c r="H250" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="I250" s="1"/>
       <x:c r="J250" s="1"/>
@@ -10474,7 +10429,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B251" s="1" t="s">
-        <x:v>518</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="C251" s="1" t="str">
         <x:v>CAMBODIA ED ORD - ស្ថានភាពលក់</x:v>
@@ -10499,7 +10454,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B252" s="1" t="s">
-        <x:v>519</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="C252" s="1" t="str">
         <x:v>CAMBODIA ED ORD - Movement Score 0-10</x:v>
@@ -10513,7 +10468,7 @@
       <x:c r="F252" s="1"/>
       <x:c r="G252" s="1"/>
       <x:c r="H252" s="1" t="s">
-        <x:v>520</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="I252" s="1" t="s">
         <x:v>102</x:v>
@@ -10528,7 +10483,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B253" s="1" t="s">
-        <x:v>521</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="C253" s="1" t="str">
         <x:v>CAMBODIA ED ORD - Stock Status</x:v>
@@ -10544,7 +10499,7 @@
       </x:c>
       <x:c r="G253" s="1"/>
       <x:c r="H253" s="1" t="s">
-        <x:v>520</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="I253" s="1"/>
       <x:c r="J253" s="1"/>
@@ -10555,7 +10510,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B254" s="1" t="s">
-        <x:v>522</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="C254" s="1" t="str">
         <x:v>CAMBODIA ED ORD - BBE / Freshness Date</x:v>
@@ -10580,7 +10535,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B255" s="1" t="s">
-        <x:v>523</x:v>
+        <x:v>514</x:v>
       </x:c>
       <x:c r="C255" s="1" t="str">
         <x:v>CAMBODIA ED ORD - Buy In Price</x:v>
@@ -10609,7 +10564,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B256" s="1" t="s">
-        <x:v>524</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="C256" s="1" t="str">
         <x:v>CAMBODIA ED ORD - Sell Out Price</x:v>
@@ -10638,7 +10593,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B257" s="1" t="s">
-        <x:v>525</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="C257" s="1" t="str">
         <x:v>CAMBODIA ED ORD - New Outlet Purchase</x:v>
@@ -10665,7 +10620,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B258" s="1" t="s">
-        <x:v>526</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="C258" s="1" t="str">
         <x:v>CAMBODIA ED ORD - Volume (ctn)</x:v>
@@ -10711,7 +10666,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B260" s="1" t="s">
-        <x:v>527</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="C260" s="1" t="str">
         <x:v>Super Boostrong ORD</x:v>
@@ -10736,7 +10691,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B261" s="1" t="s">
-        <x:v>528</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="C261" s="1" t="str">
         <x:v>Super Boostrong ORD - ស្ថានភាពលក់</x:v>
@@ -10761,7 +10716,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B262" s="1" t="s">
-        <x:v>529</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="C262" s="1" t="str">
         <x:v>Super Boostrong ORD - Movement Score 0-10</x:v>
@@ -10775,7 +10730,7 @@
       <x:c r="F262" s="1"/>
       <x:c r="G262" s="1"/>
       <x:c r="H262" s="1" t="s">
-        <x:v>530</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="I262" s="1" t="s">
         <x:v>102</x:v>
@@ -10790,7 +10745,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B263" s="1" t="s">
-        <x:v>531</x:v>
+        <x:v>522</x:v>
       </x:c>
       <x:c r="C263" s="1" t="str">
         <x:v>Super Boostrong ORD - Stock Status</x:v>
@@ -10817,7 +10772,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B264" s="1" t="s">
-        <x:v>532</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="C264" s="1" t="str">
         <x:v>Super Boostrong ORD - Buy In Price</x:v>
@@ -10846,7 +10801,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B265" s="1" t="s">
-        <x:v>533</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="C265" s="1" t="str">
         <x:v>Super Boostrong ORD - Sell Out Price</x:v>
@@ -10892,7 +10847,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B267" s="1" t="s">
-        <x:v>534</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="C267" s="1" t="str">
         <x:v>King Kong ORD</x:v>
@@ -10917,7 +10872,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B268" s="1" t="s">
-        <x:v>535</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="C268" s="1" t="str">
         <x:v>King Kong ORD - ស្ថានភាពលក់</x:v>
@@ -10942,7 +10897,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B269" s="1" t="s">
-        <x:v>536</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="C269" s="1" t="str">
         <x:v>King Kong ORD - Movement Score 0-10</x:v>
@@ -10956,7 +10911,7 @@
       <x:c r="F269" s="1"/>
       <x:c r="G269" s="1"/>
       <x:c r="H269" s="1" t="s">
-        <x:v>537</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="I269" s="1" t="s">
         <x:v>102</x:v>
@@ -10971,7 +10926,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B270" s="1" t="s">
-        <x:v>538</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="C270" s="1" t="str">
         <x:v>King Kong ORD - Stock Status</x:v>
@@ -10998,7 +10953,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B271" s="1" t="s">
-        <x:v>539</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="C271" s="1" t="str">
         <x:v>King Kong ORD - Buy In Price</x:v>
@@ -11027,7 +10982,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B272" s="1" t="s">
-        <x:v>540</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="C272" s="1" t="str">
         <x:v>King Kong ORD - Sell Out Price</x:v>
@@ -11073,10 +11028,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B274" s="1" t="s">
-        <x:v>541</x:v>
+        <x:v>532</x:v>
       </x:c>
       <x:c r="C274" s="1" t="s">
-        <x:v>542</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="D274" s="1" t="s">
         <x:v>14</x:v>
@@ -11098,10 +11053,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B275" s="1" t="s">
-        <x:v>543</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="C275" s="1" t="s">
-        <x:v>544</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D275" s="1" t="s">
         <x:v>14</x:v>
@@ -11123,10 +11078,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B276" s="1" t="s">
-        <x:v>545</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="C276" s="1" t="s">
-        <x:v>546</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="D276" s="1" t="s">
         <x:v>14</x:v>
@@ -11137,7 +11092,7 @@
       <x:c r="F276" s="1"/>
       <x:c r="G276" s="1"/>
       <x:c r="H276" s="1" t="s">
-        <x:v>547</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="I276" s="1" t="s">
         <x:v>102</x:v>
@@ -11152,10 +11107,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B277" s="1" t="s">
-        <x:v>548</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="C277" s="1" t="s">
-        <x:v>549</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="D277" s="1" t="s">
         <x:v>14</x:v>
@@ -11179,10 +11134,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B278" s="1" t="s">
-        <x:v>550</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="C278" s="1" t="s">
-        <x:v>551</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="D278" s="1" t="s">
         <x:v>14</x:v>
@@ -11208,10 +11163,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B279" s="1" t="s">
-        <x:v>552</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="C279" s="1" t="s">
-        <x:v>553</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="D279" s="1" t="s">
         <x:v>14</x:v>
@@ -11254,7 +11209,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B281" s="1" t="s">
-        <x:v>554</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="C281" s="1" t="str">
         <x:v>DAZZ ORD</x:v>
@@ -11279,7 +11234,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B282" s="1" t="s">
-        <x:v>555</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="C282" s="1" t="str">
         <x:v>DAZZ ORD - ស្ថានភាពលក់</x:v>
@@ -11304,7 +11259,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B283" s="1" t="s">
-        <x:v>556</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="C283" s="1" t="str">
         <x:v>DAZZ ORD - Movement Score 0-10</x:v>
@@ -11318,7 +11273,7 @@
       <x:c r="F283" s="1"/>
       <x:c r="G283" s="1"/>
       <x:c r="H283" s="1" t="s">
-        <x:v>557</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="I283" s="1" t="s">
         <x:v>102</x:v>
@@ -11333,7 +11288,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B284" s="1" t="s">
-        <x:v>558</x:v>
+        <x:v>549</x:v>
       </x:c>
       <x:c r="C284" s="1" t="str">
         <x:v>DAZZ ORD - Stock Status</x:v>
@@ -11360,7 +11315,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B285" s="1" t="s">
-        <x:v>559</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="C285" s="1" t="str">
         <x:v>DAZZ ORD - BBE / Freshness Date</x:v>
@@ -11385,7 +11340,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B286" s="1" t="s">
-        <x:v>560</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="C286" s="1" t="str">
         <x:v>DAZZ ORD - Buy In Price</x:v>
@@ -11414,7 +11369,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B287" s="1" t="s">
-        <x:v>561</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="C287" s="1" t="str">
         <x:v>DAZZ ORD - Sell Out Price</x:v>
@@ -11443,7 +11398,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B288" s="1" t="s">
-        <x:v>562</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="C288" s="1" t="str">
         <x:v>DAZZ ORD - New Outlet Purchase</x:v>
@@ -11470,7 +11425,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B289" s="1" t="s">
-        <x:v>563</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="C289" s="1" t="str">
         <x:v>DAZZ ORD - Volume (ctn)</x:v>
@@ -11516,10 +11471,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B291" s="1" t="s">
-        <x:v>564</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="C291" s="1" t="s">
-        <x:v>565</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D291" s="1" t="s">
         <x:v>14</x:v>
@@ -11541,10 +11496,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B292" s="1" t="s">
-        <x:v>566</x:v>
+        <x:v>557</x:v>
       </x:c>
       <x:c r="C292" s="1" t="s">
-        <x:v>567</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="D292" s="1" t="s">
         <x:v>14</x:v>
@@ -11566,10 +11521,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B293" s="1" t="s">
-        <x:v>568</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="C293" s="1" t="s">
-        <x:v>569</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="D293" s="1" t="s">
         <x:v>14</x:v>
@@ -11580,7 +11535,7 @@
       <x:c r="F293" s="1"/>
       <x:c r="G293" s="1"/>
       <x:c r="H293" s="1" t="s">
-        <x:v>570</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="I293" s="1" t="s">
         <x:v>102</x:v>
@@ -11595,10 +11550,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B294" s="1" t="s">
-        <x:v>571</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="C294" s="1" t="s">
-        <x:v>572</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="D294" s="1" t="s">
         <x:v>14</x:v>
@@ -11622,10 +11577,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B295" s="1" t="s">
-        <x:v>573</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="C295" s="1" t="s">
-        <x:v>574</x:v>
+        <x:v>565</x:v>
       </x:c>
       <x:c r="D295" s="1" t="s">
         <x:v>14</x:v>
@@ -11651,10 +11606,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B296" s="1" t="s">
-        <x:v>575</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="C296" s="1" t="s">
-        <x:v>576</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="D296" s="1" t="s">
         <x:v>14</x:v>
@@ -11697,10 +11652,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B298" s="1" t="s">
-        <x:v>577</x:v>
-      </x:c>
-      <x:c r="C298" s="1" t="s">
-        <x:v>578</x:v>
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="C298" s="1" t="str">
+        <x:v>Dragon ORD</x:v>
       </x:c>
       <x:c r="D298" s="1" t="s">
         <x:v>14</x:v>
@@ -11722,10 +11677,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B299" s="1" t="s">
-        <x:v>579</x:v>
-      </x:c>
-      <x:c r="C299" s="1" t="s">
-        <x:v>580</x:v>
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="C299" s="1" t="str">
+        <x:v>Dragon ORD - ស្ថានភាពលក់</x:v>
       </x:c>
       <x:c r="D299" s="1" t="s">
         <x:v>14</x:v>
@@ -11747,10 +11702,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B300" s="1" t="s">
-        <x:v>581</x:v>
-      </x:c>
-      <x:c r="C300" s="1" t="s">
-        <x:v>582</x:v>
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="C300" s="1" t="str">
+        <x:v>Dragon ORD - Movement Score 0-10</x:v>
       </x:c>
       <x:c r="D300" s="1" t="s">
         <x:v>14</x:v>
@@ -11761,7 +11716,7 @@
       <x:c r="F300" s="1"/>
       <x:c r="G300" s="1"/>
       <x:c r="H300" s="1" t="s">
-        <x:v>583</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="I300" s="1" t="s">
         <x:v>102</x:v>
@@ -11776,10 +11731,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B301" s="1" t="s">
-        <x:v>584</x:v>
-      </x:c>
-      <x:c r="C301" s="1" t="s">
-        <x:v>585</x:v>
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="C301" s="1" t="str">
+        <x:v>Dragon ORD - Stock Status</x:v>
       </x:c>
       <x:c r="D301" s="1" t="s">
         <x:v>14</x:v>
@@ -11803,10 +11758,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B302" s="1" t="s">
-        <x:v>586</x:v>
-      </x:c>
-      <x:c r="C302" s="1" t="s">
-        <x:v>587</x:v>
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="C302" s="1" t="str">
+        <x:v>Dragon ORD - Buy In Price</x:v>
       </x:c>
       <x:c r="D302" s="1" t="s">
         <x:v>14</x:v>
@@ -11832,10 +11787,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B303" s="1" t="s">
-        <x:v>588</x:v>
-      </x:c>
-      <x:c r="C303" s="1" t="s">
-        <x:v>589</x:v>
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="C303" s="1" t="str">
+        <x:v>Dragon ORD - Sell Out Price</x:v>
       </x:c>
       <x:c r="D303" s="1" t="s">
         <x:v>14</x:v>
@@ -11878,7 +11833,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B305" s="1" t="s">
-        <x:v>590</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="C305" s="1" t="str">
         <x:v>DAZZ Zero Sugar ORD</x:v>
@@ -11903,7 +11858,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B306" s="1" t="s">
-        <x:v>591</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="C306" s="1" t="str">
         <x:v>DAZZ Zero Sugar ORD - ស្ថានភាពលក់</x:v>
@@ -11928,7 +11883,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B307" s="1" t="s">
-        <x:v>592</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="C307" s="1" t="str">
         <x:v>DAZZ Zero Sugar ORD - Movement Score 0-10</x:v>
@@ -11942,7 +11897,7 @@
       <x:c r="F307" s="1"/>
       <x:c r="G307" s="1"/>
       <x:c r="H307" s="1" t="s">
-        <x:v>593</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="I307" s="1" t="s">
         <x:v>102</x:v>
@@ -11957,7 +11912,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B308" s="1" t="s">
-        <x:v>594</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="C308" s="1" t="str">
         <x:v>DAZZ Zero Sugar ORD - Stock Status</x:v>
@@ -11984,7 +11939,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B309" s="1" t="s">
-        <x:v>595</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="C309" s="1" t="str">
         <x:v>DAZZ Zero Sugar ORD - BBE / Freshness Date</x:v>
@@ -12009,7 +11964,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B310" s="1" t="s">
-        <x:v>596</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="C310" s="1" t="str">
         <x:v>DAZZ Zero Sugar ORD - Buy In Price</x:v>
@@ -12038,7 +11993,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B311" s="1" t="s">
-        <x:v>597</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="C311" s="1" t="str">
         <x:v>DAZZ Zero Sugar ORD - Sell Out Price</x:v>
@@ -12067,7 +12022,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B312" s="1" t="s">
-        <x:v>598</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="C312" s="1" t="str">
         <x:v>DAZZ Zero Sugar ORD - New Outlet Purchase</x:v>
@@ -12094,7 +12049,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B313" s="1" t="s">
-        <x:v>599</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="C313" s="1" t="str">
         <x:v>DAZZ Zero Sugar ORD - Volume (ctn)</x:v>
@@ -12140,10 +12095,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B315" s="1" t="s">
-        <x:v>600</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="C315" s="1" t="s">
-        <x:v>601</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="D315" s="1" t="s">
         <x:v>14</x:v>
@@ -12165,10 +12120,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B316" s="1" t="s">
-        <x:v>602</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="C316" s="1" t="s">
-        <x:v>603</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="D316" s="1" t="s">
         <x:v>14</x:v>
@@ -12190,10 +12145,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B317" s="1" t="s">
-        <x:v>604</x:v>
+        <x:v>589</x:v>
       </x:c>
       <x:c r="C317" s="1" t="s">
-        <x:v>605</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="D317" s="1" t="s">
         <x:v>14</x:v>
@@ -12204,7 +12159,7 @@
       <x:c r="F317" s="1"/>
       <x:c r="G317" s="1"/>
       <x:c r="H317" s="1" t="s">
-        <x:v>606</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="I317" s="1" t="s">
         <x:v>102</x:v>
@@ -12219,10 +12174,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B318" s="1" t="s">
-        <x:v>607</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="C318" s="1" t="s">
-        <x:v>608</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="D318" s="1" t="s">
         <x:v>14</x:v>
@@ -12246,10 +12201,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B319" s="1" t="s">
-        <x:v>609</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="C319" s="1" t="s">
-        <x:v>610</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="D319" s="1" t="s">
         <x:v>14</x:v>
@@ -12275,10 +12230,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B320" s="1" t="s">
-        <x:v>611</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="C320" s="1" t="s">
-        <x:v>612</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="D320" s="1" t="s">
         <x:v>14</x:v>
@@ -12321,7 +12276,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B322" s="1" t="s">
-        <x:v>613</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="C322" s="1" t="str">
         <x:v>Wurkz Ice ORD</x:v>
@@ -12335,7 +12290,7 @@
       </x:c>
       <x:c r="G322" s="1"/>
       <x:c r="H322" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="I322" s="1"/>
       <x:c r="J322" s="1"/>
@@ -12346,7 +12301,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B323" s="1" t="s">
-        <x:v>614</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="C323" s="1" t="str">
         <x:v>Wurkz Ice ORD - ស្ថានភាពលក់</x:v>
@@ -12371,7 +12326,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B324" s="1" t="s">
-        <x:v>615</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="C324" s="1" t="str">
         <x:v>Wurkz Ice ORD - Movement Score 0-10</x:v>
@@ -12385,7 +12340,7 @@
       <x:c r="F324" s="1"/>
       <x:c r="G324" s="1"/>
       <x:c r="H324" s="1" t="s">
-        <x:v>616</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="I324" s="1" t="s">
         <x:v>102</x:v>
@@ -12400,7 +12355,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B325" s="1" t="s">
-        <x:v>617</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="C325" s="1" t="str">
         <x:v>Wurkz Ice ORD - Stock Status</x:v>
@@ -12427,7 +12382,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B326" s="1" t="s">
-        <x:v>618</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="C326" s="1" t="str">
         <x:v>Wurkz Ice ORD - BBE / Freshness Date</x:v>
@@ -12452,7 +12407,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B327" s="1" t="s">
-        <x:v>619</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="C327" s="1" t="str">
         <x:v>Wurkz Ice ORD - Buy In Price</x:v>
@@ -12481,7 +12436,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B328" s="1" t="s">
-        <x:v>620</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C328" s="1" t="str">
         <x:v>Wurkz Ice ORD - Sell Out Price</x:v>
@@ -12510,7 +12465,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B329" s="1" t="s">
-        <x:v>621</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="C329" s="1" t="str">
         <x:v>Wurkz Ice ORD - New Outlet Purchase</x:v>
@@ -12537,7 +12492,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B330" s="1" t="s">
-        <x:v>622</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="C330" s="1" t="str">
         <x:v>Wurkz Ice ORD - Volume (ctn)</x:v>
@@ -12583,7 +12538,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B332" s="1" t="s">
-        <x:v>623</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="C332" s="1" t="str">
         <x:v>Champion ORD</x:v>
@@ -12597,7 +12552,7 @@
       </x:c>
       <x:c r="G332" s="1"/>
       <x:c r="H332" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="I332" s="1"/>
       <x:c r="J332" s="1"/>
@@ -12608,7 +12563,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B333" s="1" t="s">
-        <x:v>624</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="C333" s="1" t="str">
         <x:v>Champion ORD - ស្ថានភាពលក់</x:v>
@@ -12633,7 +12588,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B334" s="1" t="s">
-        <x:v>625</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="C334" s="1" t="str">
         <x:v>Champion ORD - Movement Score 0-10</x:v>
@@ -12647,7 +12602,7 @@
       <x:c r="F334" s="1"/>
       <x:c r="G334" s="1"/>
       <x:c r="H334" s="1" t="s">
-        <x:v>626</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="I334" s="1" t="s">
         <x:v>102</x:v>
@@ -12662,7 +12617,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B335" s="1" t="s">
-        <x:v>627</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="C335" s="1" t="str">
         <x:v>Champion ORD - Stock Status</x:v>
@@ -12689,7 +12644,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B336" s="1" t="s">
-        <x:v>628</x:v>
+        <x:v>613</x:v>
       </x:c>
       <x:c r="C336" s="1" t="str">
         <x:v>Champion ORD - Buy In Price</x:v>
@@ -12718,7 +12673,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B337" s="1" t="s">
-        <x:v>629</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="C337" s="1" t="str">
         <x:v>Champion ORD - Sell Out Price</x:v>
@@ -12764,7 +12719,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B339" s="1" t="s">
-        <x:v>630</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="C339" s="1" t="str">
         <x:v>King Kong Ice ORD</x:v>
@@ -12778,7 +12733,7 @@
       </x:c>
       <x:c r="G339" s="1"/>
       <x:c r="H339" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="I339" s="1"/>
       <x:c r="J339" s="1"/>
@@ -12789,7 +12744,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B340" s="1" t="s">
-        <x:v>631</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="C340" s="1" t="str">
         <x:v>King Kong Ice ORD - ស្ថានភាពលក់</x:v>
@@ -12814,7 +12769,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B341" s="1" t="s">
-        <x:v>632</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="C341" s="1" t="str">
         <x:v>King Kong Ice ORD - Movement Score 0-10</x:v>
@@ -12828,7 +12783,7 @@
       <x:c r="F341" s="1"/>
       <x:c r="G341" s="1"/>
       <x:c r="H341" s="1" t="s">
-        <x:v>633</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="I341" s="1" t="s">
         <x:v>102</x:v>
@@ -12843,7 +12798,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B342" s="1" t="s">
-        <x:v>634</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="C342" s="1" t="str">
         <x:v>King Kong Ice ORD - Stock Status</x:v>
@@ -12870,7 +12825,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B343" s="1" t="s">
-        <x:v>635</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="C343" s="1" t="str">
         <x:v>King Kong Ice ORD - Buy In Price</x:v>
@@ -12899,7 +12854,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B344" s="1" t="s">
-        <x:v>636</x:v>
+        <x:v>621</x:v>
       </x:c>
       <x:c r="C344" s="1" t="str">
         <x:v>King Kong Ice ORD - Sell Out Price</x:v>
@@ -12945,7 +12900,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B346" s="1" t="s">
-        <x:v>637</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="C346" s="1" t="str">
         <x:v>Krud Ice ORD</x:v>
@@ -12959,7 +12914,7 @@
       </x:c>
       <x:c r="G346" s="1"/>
       <x:c r="H346" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="I346" s="1"/>
       <x:c r="J346" s="1"/>
@@ -12970,7 +12925,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B347" s="1" t="s">
-        <x:v>638</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="C347" s="1" t="str">
         <x:v>Krud Ice ORD - ស្ថានភាពលក់</x:v>
@@ -12995,7 +12950,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B348" s="1" t="s">
-        <x:v>639</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="C348" s="1" t="str">
         <x:v>Krud Ice ORD - Movement Score 0-10</x:v>
@@ -13009,7 +12964,7 @@
       <x:c r="F348" s="1"/>
       <x:c r="G348" s="1"/>
       <x:c r="H348" s="1" t="s">
-        <x:v>640</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="I348" s="1" t="s">
         <x:v>102</x:v>
@@ -13024,7 +12979,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B349" s="1" t="s">
-        <x:v>641</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="C349" s="1" t="str">
         <x:v>Krud Ice ORD - Stock Status</x:v>
@@ -13051,7 +13006,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B350" s="1" t="s">
-        <x:v>642</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="C350" s="1" t="str">
         <x:v>Krud Ice ORD - Buy In Price</x:v>
@@ -13080,7 +13035,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B351" s="1" t="s">
-        <x:v>643</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="C351" s="1" t="str">
         <x:v>Krud Ice ORD - Sell Out Price</x:v>
@@ -13126,10 +13081,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B353" s="1" t="s">
-        <x:v>644</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="C353" s="1" t="s">
-        <x:v>645</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="D353" s="1" t="s">
         <x:v>14</x:v>
@@ -13140,7 +13095,7 @@
       </x:c>
       <x:c r="G353" s="1"/>
       <x:c r="H353" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="I353" s="1"/>
       <x:c r="J353" s="1"/>
@@ -13151,10 +13106,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B354" s="1" t="s">
-        <x:v>646</x:v>
+        <x:v>631</x:v>
       </x:c>
       <x:c r="C354" s="1" t="s">
-        <x:v>647</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="D354" s="1" t="s">
         <x:v>14</x:v>
@@ -13176,10 +13131,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B355" s="1" t="s">
-        <x:v>648</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="C355" s="1" t="s">
-        <x:v>649</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="D355" s="1" t="s">
         <x:v>14</x:v>
@@ -13190,7 +13145,7 @@
       <x:c r="F355" s="1"/>
       <x:c r="G355" s="1"/>
       <x:c r="H355" s="1" t="s">
-        <x:v>650</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="I355" s="1" t="s">
         <x:v>102</x:v>
@@ -13205,10 +13160,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B356" s="1" t="s">
-        <x:v>651</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="C356" s="1" t="s">
-        <x:v>652</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="D356" s="1" t="s">
         <x:v>14</x:v>
@@ -13232,10 +13187,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B357" s="1" t="s">
-        <x:v>653</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="C357" s="1" t="s">
-        <x:v>654</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="D357" s="1" t="s">
         <x:v>14</x:v>
@@ -13257,10 +13212,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B358" s="1" t="s">
-        <x:v>655</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="C358" s="1" t="s">
-        <x:v>656</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="D358" s="1" t="s">
         <x:v>14</x:v>
@@ -13286,10 +13241,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B359" s="1" t="s">
-        <x:v>657</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="C359" s="1" t="s">
-        <x:v>658</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="D359" s="1" t="s">
         <x:v>14</x:v>
@@ -13315,10 +13270,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B360" s="1" t="s">
-        <x:v>659</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="C360" s="1" t="s">
-        <x:v>660</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="D360" s="1" t="s">
         <x:v>14</x:v>
@@ -13342,10 +13297,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B361" s="1" t="s">
-        <x:v>661</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="C361" s="1" t="s">
-        <x:v>662</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="D361" s="1" t="s">
         <x:v>14</x:v>
@@ -13388,10 +13343,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B363" s="1" t="s">
-        <x:v>663</x:v>
+        <x:v>648</x:v>
       </x:c>
       <x:c r="C363" s="1" t="s">
-        <x:v>664</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="D363" s="1" t="s">
         <x:v>14</x:v>
@@ -13402,7 +13357,7 @@
       </x:c>
       <x:c r="G363" s="1"/>
       <x:c r="H363" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="I363" s="1"/>
       <x:c r="J363" s="1"/>
@@ -13413,10 +13368,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B364" s="1" t="s">
-        <x:v>665</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="C364" s="1" t="s">
-        <x:v>666</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="D364" s="1" t="s">
         <x:v>14</x:v>
@@ -13438,10 +13393,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B365" s="1" t="s">
-        <x:v>667</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="C365" s="1" t="s">
-        <x:v>668</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="D365" s="1" t="s">
         <x:v>14</x:v>
@@ -13452,7 +13407,7 @@
       <x:c r="F365" s="1"/>
       <x:c r="G365" s="1"/>
       <x:c r="H365" s="1" t="s">
-        <x:v>669</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="I365" s="1" t="s">
         <x:v>102</x:v>
@@ -13467,10 +13422,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B366" s="1" t="s">
-        <x:v>670</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="C366" s="1" t="s">
-        <x:v>671</x:v>
+        <x:v>656</x:v>
       </x:c>
       <x:c r="D366" s="1" t="s">
         <x:v>14</x:v>
@@ -13494,10 +13449,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B367" s="1" t="s">
-        <x:v>672</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="C367" s="1" t="s">
-        <x:v>673</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="D367" s="1" t="s">
         <x:v>14</x:v>
@@ -13523,10 +13478,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B368" s="1" t="s">
-        <x:v>674</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="C368" s="1" t="s">
-        <x:v>675</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="D368" s="1" t="s">
         <x:v>14</x:v>
@@ -13569,10 +13524,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B370" s="1" t="s">
-        <x:v>676</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="C370" s="1" t="s">
-        <x:v>677</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="D370" s="1" t="s">
         <x:v>14</x:v>
@@ -13583,7 +13538,7 @@
       </x:c>
       <x:c r="G370" s="1"/>
       <x:c r="H370" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="I370" s="1"/>
       <x:c r="J370" s="1"/>
@@ -13594,10 +13549,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B371" s="1" t="s">
-        <x:v>678</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="C371" s="1" t="s">
-        <x:v>679</x:v>
+        <x:v>664</x:v>
       </x:c>
       <x:c r="D371" s="1" t="s">
         <x:v>14</x:v>
@@ -13619,10 +13574,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B372" s="1" t="s">
-        <x:v>680</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="C372" s="1" t="s">
-        <x:v>681</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="D372" s="1" t="s">
         <x:v>14</x:v>
@@ -13633,7 +13588,7 @@
       <x:c r="F372" s="1"/>
       <x:c r="G372" s="1"/>
       <x:c r="H372" s="1" t="s">
-        <x:v>682</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="I372" s="1" t="s">
         <x:v>102</x:v>
@@ -13648,10 +13603,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B373" s="1" t="s">
-        <x:v>683</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="C373" s="1" t="s">
-        <x:v>684</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="D373" s="1" t="s">
         <x:v>14</x:v>
@@ -13675,10 +13630,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B374" s="1" t="s">
-        <x:v>685</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="C374" s="1" t="s">
-        <x:v>686</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="D374" s="1" t="s">
         <x:v>14</x:v>
@@ -13704,10 +13659,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B375" s="1" t="s">
-        <x:v>687</x:v>
+        <x:v>672</x:v>
       </x:c>
       <x:c r="C375" s="1" t="s">
-        <x:v>688</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="D375" s="1" t="s">
         <x:v>14</x:v>
@@ -13750,10 +13705,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B377" s="1" t="s">
-        <x:v>689</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="C377" s="1" t="s">
-        <x:v>690</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="D377" s="1" t="s">
         <x:v>14</x:v>
@@ -13764,7 +13719,7 @@
       </x:c>
       <x:c r="G377" s="1"/>
       <x:c r="H377" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="I377" s="1"/>
       <x:c r="J377" s="1"/>
@@ -13775,10 +13730,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B378" s="1" t="s">
-        <x:v>691</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="C378" s="1" t="s">
-        <x:v>692</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="D378" s="1" t="s">
         <x:v>14</x:v>
@@ -13800,10 +13755,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B379" s="1" t="s">
-        <x:v>693</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="C379" s="1" t="s">
-        <x:v>694</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="D379" s="1" t="s">
         <x:v>14</x:v>
@@ -13814,7 +13769,7 @@
       <x:c r="F379" s="1"/>
       <x:c r="G379" s="1"/>
       <x:c r="H379" s="1" t="s">
-        <x:v>695</x:v>
+        <x:v>680</x:v>
       </x:c>
       <x:c r="I379" s="1" t="s">
         <x:v>102</x:v>
@@ -13829,10 +13784,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B380" s="1" t="s">
-        <x:v>696</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="C380" s="1" t="s">
-        <x:v>697</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="D380" s="1" t="s">
         <x:v>14</x:v>
@@ -13856,10 +13811,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B381" s="1" t="s">
-        <x:v>698</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="C381" s="1" t="s">
-        <x:v>699</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="D381" s="1" t="s">
         <x:v>14</x:v>
@@ -13881,10 +13836,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B382" s="1" t="s">
-        <x:v>700</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="C382" s="1" t="s">
-        <x:v>701</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="D382" s="1" t="s">
         <x:v>14</x:v>
@@ -13910,10 +13865,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B383" s="1" t="s">
-        <x:v>702</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="C383" s="1" t="s">
-        <x:v>703</x:v>
+        <x:v>688</x:v>
       </x:c>
       <x:c r="D383" s="1" t="s">
         <x:v>14</x:v>
@@ -13939,10 +13894,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B384" s="1" t="s">
-        <x:v>704</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="C384" s="1" t="s">
-        <x:v>705</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="D384" s="1" t="s">
         <x:v>14</x:v>
@@ -13966,10 +13921,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B385" s="1" t="s">
-        <x:v>706</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="C385" s="1" t="s">
-        <x:v>707</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="D385" s="1" t="s">
         <x:v>14</x:v>
@@ -14012,10 +13967,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B387" s="1" t="s">
-        <x:v>708</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="C387" s="1" t="s">
-        <x:v>709</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="D387" s="1" t="s">
         <x:v>14</x:v>
@@ -14026,7 +13981,7 @@
       </x:c>
       <x:c r="G387" s="1"/>
       <x:c r="H387" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="I387" s="1"/>
       <x:c r="J387" s="1"/>
@@ -14037,10 +13992,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B388" s="1" t="s">
-        <x:v>710</x:v>
+        <x:v>695</x:v>
       </x:c>
       <x:c r="C388" s="1" t="s">
-        <x:v>711</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="D388" s="1" t="s">
         <x:v>14</x:v>
@@ -14062,10 +14017,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B389" s="1" t="s">
-        <x:v>712</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="C389" s="1" t="s">
-        <x:v>713</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="D389" s="1" t="s">
         <x:v>14</x:v>
@@ -14076,7 +14031,7 @@
       <x:c r="F389" s="1"/>
       <x:c r="G389" s="1"/>
       <x:c r="H389" s="1" t="s">
-        <x:v>714</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="I389" s="1" t="s">
         <x:v>102</x:v>
@@ -14091,10 +14046,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B390" s="1" t="s">
-        <x:v>715</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="C390" s="1" t="s">
-        <x:v>716</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="D390" s="1" t="s">
         <x:v>14</x:v>
@@ -14118,10 +14073,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B391" s="1" t="s">
-        <x:v>717</x:v>
+        <x:v>702</x:v>
       </x:c>
       <x:c r="C391" s="1" t="s">
-        <x:v>718</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="D391" s="1" t="s">
         <x:v>14</x:v>
@@ -14147,10 +14102,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B392" s="1" t="s">
-        <x:v>719</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="C392" s="1" t="s">
-        <x:v>720</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="D392" s="1" t="s">
         <x:v>14</x:v>
@@ -14193,10 +14148,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B394" s="1" t="s">
-        <x:v>721</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="C394" s="1" t="s">
-        <x:v>722</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="D394" s="1" t="s">
         <x:v>14</x:v>
@@ -14207,7 +14162,7 @@
       </x:c>
       <x:c r="G394" s="1"/>
       <x:c r="H394" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="I394" s="1"/>
       <x:c r="J394" s="1"/>
@@ -14218,10 +14173,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B395" s="1" t="s">
-        <x:v>723</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="C395" s="1" t="s">
-        <x:v>724</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="D395" s="1" t="s">
         <x:v>14</x:v>
@@ -14243,10 +14198,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B396" s="1" t="s">
-        <x:v>725</x:v>
+        <x:v>710</x:v>
       </x:c>
       <x:c r="C396" s="1" t="s">
-        <x:v>726</x:v>
+        <x:v>711</x:v>
       </x:c>
       <x:c r="D396" s="1" t="s">
         <x:v>14</x:v>
@@ -14257,7 +14212,7 @@
       <x:c r="F396" s="1"/>
       <x:c r="G396" s="1"/>
       <x:c r="H396" s="1" t="s">
-        <x:v>727</x:v>
+        <x:v>712</x:v>
       </x:c>
       <x:c r="I396" s="1" t="s">
         <x:v>102</x:v>
@@ -14272,10 +14227,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B397" s="1" t="s">
-        <x:v>728</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="C397" s="1" t="s">
-        <x:v>729</x:v>
+        <x:v>714</x:v>
       </x:c>
       <x:c r="D397" s="1" t="s">
         <x:v>14</x:v>
@@ -14299,10 +14254,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B398" s="1" t="s">
-        <x:v>730</x:v>
+        <x:v>715</x:v>
       </x:c>
       <x:c r="C398" s="1" t="s">
-        <x:v>731</x:v>
+        <x:v>716</x:v>
       </x:c>
       <x:c r="D398" s="1" t="s">
         <x:v>14</x:v>
@@ -14328,10 +14283,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B399" s="1" t="s">
-        <x:v>732</x:v>
+        <x:v>717</x:v>
       </x:c>
       <x:c r="C399" s="1" t="s">
-        <x:v>733</x:v>
+        <x:v>718</x:v>
       </x:c>
       <x:c r="D399" s="1" t="s">
         <x:v>14</x:v>
@@ -14374,7 +14329,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B401" s="1" t="s">
-        <x:v>734</x:v>
+        <x:v>719</x:v>
       </x:c>
       <x:c r="C401" s="1" t="str">
         <x:v>EXPREZ Melon ORD</x:v>
@@ -14399,7 +14354,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B402" s="1" t="s">
-        <x:v>735</x:v>
+        <x:v>720</x:v>
       </x:c>
       <x:c r="C402" s="1" t="str">
         <x:v>EXPREZ Melon ORD - ស្ថានភាពលក់</x:v>
@@ -14424,7 +14379,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B403" s="1" t="s">
-        <x:v>736</x:v>
+        <x:v>721</x:v>
       </x:c>
       <x:c r="C403" s="1" t="str">
         <x:v>EXPREZ Melon ORD - Movement Score 0-10</x:v>
@@ -14438,7 +14393,7 @@
       <x:c r="F403" s="1"/>
       <x:c r="G403" s="1"/>
       <x:c r="H403" s="1" t="s">
-        <x:v>737</x:v>
+        <x:v>722</x:v>
       </x:c>
       <x:c r="I403" s="1" t="s">
         <x:v>102</x:v>
@@ -14453,7 +14408,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B404" s="1" t="s">
-        <x:v>738</x:v>
+        <x:v>723</x:v>
       </x:c>
       <x:c r="C404" s="1" t="str">
         <x:v>EXPREZ Melon ORD - Stock Status</x:v>
@@ -14480,7 +14435,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B405" s="1" t="s">
-        <x:v>739</x:v>
+        <x:v>724</x:v>
       </x:c>
       <x:c r="C405" s="1" t="str">
         <x:v>EXPREZ Melon ORD - BBE / Freshness Date</x:v>
@@ -14505,7 +14460,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B406" s="1" t="s">
-        <x:v>740</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="C406" s="1" t="str">
         <x:v>EXPREZ Melon ORD - Buy In Price</x:v>
@@ -14534,7 +14489,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B407" s="1" t="s">
-        <x:v>741</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="C407" s="1" t="str">
         <x:v>EXPREZ Melon ORD - Sell Out Price</x:v>
@@ -14563,7 +14518,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B408" s="1" t="s">
-        <x:v>742</x:v>
+        <x:v>727</x:v>
       </x:c>
       <x:c r="C408" s="1" t="str">
         <x:v>EXPREZ Melon ORD - New Outlet Purchase</x:v>
@@ -14590,7 +14545,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B409" s="1" t="s">
-        <x:v>743</x:v>
+        <x:v>728</x:v>
       </x:c>
       <x:c r="C409" s="1" t="str">
         <x:v>EXPREZ Melon ORD - Volume (ctn)</x:v>
@@ -14636,7 +14591,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B411" s="1" t="s">
-        <x:v>744</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="C411" s="1" t="str">
         <x:v>EXPREZ Can 330ml ORD</x:v>
@@ -14661,7 +14616,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B412" s="1" t="s">
-        <x:v>745</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="C412" s="1" t="str">
         <x:v>EXPREZ Can 330ml ORD - ស្ថានភាពលក់</x:v>
@@ -14686,7 +14641,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B413" s="1" t="s">
-        <x:v>746</x:v>
+        <x:v>731</x:v>
       </x:c>
       <x:c r="C413" s="1" t="str">
         <x:v>EXPREZ Can 330ml ORD - Movement Score 0-10</x:v>
@@ -14700,7 +14655,7 @@
       <x:c r="F413" s="1"/>
       <x:c r="G413" s="1"/>
       <x:c r="H413" s="1" t="s">
-        <x:v>747</x:v>
+        <x:v>732</x:v>
       </x:c>
       <x:c r="I413" s="1" t="s">
         <x:v>102</x:v>
@@ -14715,7 +14670,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B414" s="1" t="s">
-        <x:v>748</x:v>
+        <x:v>733</x:v>
       </x:c>
       <x:c r="C414" s="1" t="str">
         <x:v>EXPREZ Can 330ml ORD - Stock Status</x:v>
@@ -14742,7 +14697,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B415" s="1" t="s">
-        <x:v>749</x:v>
+        <x:v>734</x:v>
       </x:c>
       <x:c r="C415" s="1" t="str">
         <x:v>EXPREZ Can 330ml ORD - Buy In Price</x:v>
@@ -14771,7 +14726,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B416" s="1" t="s">
-        <x:v>750</x:v>
+        <x:v>735</x:v>
       </x:c>
       <x:c r="C416" s="1" t="str">
         <x:v>EXPREZ Can 330ml ORD - Sell Out Price</x:v>
@@ -14817,10 +14772,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B418" s="1" t="s">
-        <x:v>751</x:v>
+        <x:v>736</x:v>
       </x:c>
       <x:c r="C418" s="1" t="s">
-        <x:v>752</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="D418" s="1" t="s">
         <x:v>14</x:v>
@@ -14842,10 +14797,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B419" s="1" t="s">
-        <x:v>753</x:v>
+        <x:v>738</x:v>
       </x:c>
       <x:c r="C419" s="1" t="s">
-        <x:v>754</x:v>
+        <x:v>739</x:v>
       </x:c>
       <x:c r="D419" s="1" t="s">
         <x:v>14</x:v>
@@ -14867,10 +14822,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B420" s="1" t="s">
-        <x:v>755</x:v>
+        <x:v>740</x:v>
       </x:c>
       <x:c r="C420" s="1" t="s">
-        <x:v>756</x:v>
+        <x:v>741</x:v>
       </x:c>
       <x:c r="D420" s="1" t="s">
         <x:v>14</x:v>
@@ -14881,7 +14836,7 @@
       <x:c r="F420" s="1"/>
       <x:c r="G420" s="1"/>
       <x:c r="H420" s="1" t="s">
-        <x:v>757</x:v>
+        <x:v>742</x:v>
       </x:c>
       <x:c r="I420" s="1" t="s">
         <x:v>102</x:v>
@@ -14896,10 +14851,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B421" s="1" t="s">
-        <x:v>758</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="C421" s="1" t="s">
-        <x:v>759</x:v>
+        <x:v>744</x:v>
       </x:c>
       <x:c r="D421" s="1" t="s">
         <x:v>14</x:v>
@@ -14923,10 +14878,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B422" s="1" t="s">
-        <x:v>760</x:v>
+        <x:v>745</x:v>
       </x:c>
       <x:c r="C422" s="1" t="s">
-        <x:v>761</x:v>
+        <x:v>746</x:v>
       </x:c>
       <x:c r="D422" s="1" t="s">
         <x:v>14</x:v>
@@ -14952,10 +14907,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B423" s="1" t="s">
-        <x:v>762</x:v>
+        <x:v>747</x:v>
       </x:c>
       <x:c r="C423" s="1" t="s">
-        <x:v>763</x:v>
+        <x:v>748</x:v>
       </x:c>
       <x:c r="D423" s="1" t="s">
         <x:v>14</x:v>
@@ -14998,7 +14953,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B425" s="1" t="s">
-        <x:v>764</x:v>
+        <x:v>749</x:v>
       </x:c>
       <x:c r="C425" s="1" t="str">
         <x:v>Idol Can 330ml ORD</x:v>
@@ -15023,7 +14978,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B426" s="1" t="s">
-        <x:v>765</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="C426" s="1" t="str">
         <x:v>Idol Can 330ml ORD - ស្ថានភាពលក់</x:v>
@@ -15048,7 +15003,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B427" s="1" t="s">
-        <x:v>766</x:v>
+        <x:v>751</x:v>
       </x:c>
       <x:c r="C427" s="1" t="str">
         <x:v>Idol Can 330ml ORD - Movement Score 0-10</x:v>
@@ -15062,7 +15017,7 @@
       <x:c r="F427" s="1"/>
       <x:c r="G427" s="1"/>
       <x:c r="H427" s="1" t="s">
-        <x:v>767</x:v>
+        <x:v>752</x:v>
       </x:c>
       <x:c r="I427" s="1" t="s">
         <x:v>102</x:v>
@@ -15077,7 +15032,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B428" s="1" t="s">
-        <x:v>768</x:v>
+        <x:v>753</x:v>
       </x:c>
       <x:c r="C428" s="1" t="str">
         <x:v>Idol Can 330ml ORD - Stock Status</x:v>
@@ -15104,7 +15059,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B429" s="1" t="s">
-        <x:v>769</x:v>
+        <x:v>754</x:v>
       </x:c>
       <x:c r="C429" s="1" t="str">
         <x:v>Idol Can 330ml ORD - Buy In Price</x:v>
@@ -15133,7 +15088,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B430" s="1" t="s">
-        <x:v>770</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="C430" s="1" t="str">
         <x:v>Idol Can 330ml ORD - Sell Out Price</x:v>
@@ -15309,7 +15264,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B442" s="1" t="s">
-        <x:v>771</x:v>
+        <x:v>756</x:v>
       </x:c>
       <x:c r="C442" s="1" t="str">
         <x:v>CAMBODIA Sport 500mL ORD</x:v>
@@ -15334,7 +15289,7 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B443" s="1" t="s">
-        <x:v>772</x:v>
+        <x:v>757</x:v>
       </x:c>
       <x:c r="C443" s="1" t="str">
         <x:v>CAMBODIA Sport 500mL ORD - ស្ថានភាពលក់</x:v>
@@ -15359,7 +15314,7 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B444" s="1" t="s">
-        <x:v>773</x:v>
+        <x:v>758</x:v>
       </x:c>
       <x:c r="C444" s="1" t="str">
         <x:v>CAMBODIA Sport 500mL ORD - Movement Score 0-10</x:v>
@@ -15373,7 +15328,7 @@
       <x:c r="F444" s="1"/>
       <x:c r="G444" s="1"/>
       <x:c r="H444" s="1" t="s">
-        <x:v>774</x:v>
+        <x:v>759</x:v>
       </x:c>
       <x:c r="I444" s="1" t="s">
         <x:v>102</x:v>
@@ -15388,7 +15343,7 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B445" s="1" t="s">
-        <x:v>775</x:v>
+        <x:v>760</x:v>
       </x:c>
       <x:c r="C445" s="1" t="str">
         <x:v>CAMBODIA Sport 500mL ORD - Stock Status</x:v>
@@ -15415,7 +15370,7 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B446" s="1" t="s">
-        <x:v>776</x:v>
+        <x:v>761</x:v>
       </x:c>
       <x:c r="C446" s="1" t="str">
         <x:v>CAMBODIA Sport 500mL ORD - BBE / Freshness Date</x:v>
@@ -15440,7 +15395,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B447" s="1" t="s">
-        <x:v>777</x:v>
+        <x:v>762</x:v>
       </x:c>
       <x:c r="C447" s="1" t="str">
         <x:v>CAMBODIA Sport 500mL ORD - Buy In Price</x:v>
@@ -15469,7 +15424,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B448" s="1" t="s">
-        <x:v>778</x:v>
+        <x:v>763</x:v>
       </x:c>
       <x:c r="C448" s="1" t="str">
         <x:v>CAMBODIA Sport 500mL ORD - Sell Out Price</x:v>
@@ -15498,7 +15453,7 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B449" s="1" t="s">
-        <x:v>779</x:v>
+        <x:v>764</x:v>
       </x:c>
       <x:c r="C449" s="1" t="str">
         <x:v>CAMBODIA Sport 500mL ORD - New Outlet Purchase</x:v>
@@ -15525,7 +15480,7 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B450" s="1" t="s">
-        <x:v>780</x:v>
+        <x:v>765</x:v>
       </x:c>
       <x:c r="C450" s="1" t="str">
         <x:v>CAMBODIA Sport 500mL ORD - Volume (ctn)</x:v>
@@ -15571,10 +15526,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B452" s="1" t="s">
-        <x:v>781</x:v>
+        <x:v>766</x:v>
       </x:c>
       <x:c r="C452" s="1" t="s">
-        <x:v>782</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="D452" s="1" t="s">
         <x:v>14</x:v>
@@ -15596,10 +15551,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B453" s="1" t="s">
-        <x:v>783</x:v>
+        <x:v>768</x:v>
       </x:c>
       <x:c r="C453" s="1" t="s">
-        <x:v>784</x:v>
+        <x:v>769</x:v>
       </x:c>
       <x:c r="D453" s="1" t="s">
         <x:v>14</x:v>
@@ -15621,10 +15576,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B454" s="1" t="s">
-        <x:v>785</x:v>
+        <x:v>770</x:v>
       </x:c>
       <x:c r="C454" s="1" t="s">
-        <x:v>786</x:v>
+        <x:v>771</x:v>
       </x:c>
       <x:c r="D454" s="1" t="s">
         <x:v>14</x:v>
@@ -15635,7 +15590,7 @@
       <x:c r="F454" s="1"/>
       <x:c r="G454" s="1"/>
       <x:c r="H454" s="1" t="s">
-        <x:v>787</x:v>
+        <x:v>772</x:v>
       </x:c>
       <x:c r="I454" s="1" t="s">
         <x:v>102</x:v>
@@ -15650,10 +15605,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B455" s="1" t="s">
-        <x:v>788</x:v>
+        <x:v>773</x:v>
       </x:c>
       <x:c r="C455" s="1" t="s">
-        <x:v>789</x:v>
+        <x:v>774</x:v>
       </x:c>
       <x:c r="D455" s="1" t="s">
         <x:v>14</x:v>
@@ -15677,10 +15632,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B456" s="1" t="s">
-        <x:v>790</x:v>
+        <x:v>775</x:v>
       </x:c>
       <x:c r="C456" s="1" t="s">
-        <x:v>791</x:v>
+        <x:v>776</x:v>
       </x:c>
       <x:c r="D456" s="1" t="s">
         <x:v>14</x:v>
@@ -15706,10 +15661,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B457" s="1" t="s">
-        <x:v>792</x:v>
+        <x:v>777</x:v>
       </x:c>
       <x:c r="C457" s="1" t="s">
-        <x:v>793</x:v>
+        <x:v>778</x:v>
       </x:c>
       <x:c r="D457" s="1" t="s">
         <x:v>14</x:v>
@@ -15752,10 +15707,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B459" s="1" t="s">
-        <x:v>794</x:v>
+        <x:v>779</x:v>
       </x:c>
       <x:c r="C459" s="1" t="s">
-        <x:v>795</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="D459" s="1" t="s">
         <x:v>14</x:v>
@@ -15777,10 +15732,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B460" s="1" t="s">
-        <x:v>796</x:v>
+        <x:v>781</x:v>
       </x:c>
       <x:c r="C460" s="1" t="s">
-        <x:v>797</x:v>
+        <x:v>782</x:v>
       </x:c>
       <x:c r="D460" s="1" t="s">
         <x:v>14</x:v>
@@ -15802,10 +15757,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B461" s="1" t="s">
-        <x:v>798</x:v>
+        <x:v>783</x:v>
       </x:c>
       <x:c r="C461" s="1" t="s">
-        <x:v>799</x:v>
+        <x:v>784</x:v>
       </x:c>
       <x:c r="D461" s="1" t="s">
         <x:v>14</x:v>
@@ -15816,7 +15771,7 @@
       <x:c r="F461" s="1"/>
       <x:c r="G461" s="1"/>
       <x:c r="H461" s="1" t="s">
-        <x:v>800</x:v>
+        <x:v>785</x:v>
       </x:c>
       <x:c r="I461" s="1" t="s">
         <x:v>102</x:v>
@@ -15831,10 +15786,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B462" s="1" t="s">
-        <x:v>801</x:v>
+        <x:v>786</x:v>
       </x:c>
       <x:c r="C462" s="1" t="s">
-        <x:v>802</x:v>
+        <x:v>787</x:v>
       </x:c>
       <x:c r="D462" s="1" t="s">
         <x:v>14</x:v>
@@ -15858,10 +15813,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B463" s="1" t="s">
-        <x:v>803</x:v>
+        <x:v>788</x:v>
       </x:c>
       <x:c r="C463" s="1" t="s">
-        <x:v>804</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="D463" s="1" t="s">
         <x:v>14</x:v>
@@ -15887,10 +15842,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B464" s="1" t="s">
-        <x:v>805</x:v>
+        <x:v>790</x:v>
       </x:c>
       <x:c r="C464" s="1" t="s">
-        <x:v>806</x:v>
+        <x:v>791</x:v>
       </x:c>
       <x:c r="D464" s="1" t="s">
         <x:v>14</x:v>
@@ -15933,10 +15888,10 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B466" s="1" t="s">
-        <x:v>807</x:v>
+        <x:v>792</x:v>
       </x:c>
       <x:c r="C466" s="1" t="s">
-        <x:v>808</x:v>
+        <x:v>793</x:v>
       </x:c>
       <x:c r="D466" s="1" t="s">
         <x:v>14</x:v>
@@ -15954,10 +15909,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B467" s="1" t="s">
-        <x:v>809</x:v>
+        <x:v>794</x:v>
       </x:c>
       <x:c r="C467" s="1" t="s">
-        <x:v>810</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="D467" s="1" t="s">
         <x:v>14</x:v>
@@ -15979,10 +15934,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B468" s="1" t="s">
-        <x:v>811</x:v>
+        <x:v>796</x:v>
       </x:c>
       <x:c r="C468" s="1" t="s">
-        <x:v>812</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="D468" s="1" t="s">
         <x:v>14</x:v>
@@ -16004,10 +15959,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B469" s="1" t="s">
-        <x:v>813</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="C469" s="1" t="s">
-        <x:v>814</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="D469" s="1" t="s">
         <x:v>14</x:v>
@@ -16018,7 +15973,7 @@
       <x:c r="F469" s="1"/>
       <x:c r="G469" s="1"/>
       <x:c r="H469" s="1" t="s">
-        <x:v>815</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="I469" s="1" t="s">
         <x:v>102</x:v>
@@ -16033,10 +15988,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B470" s="1" t="s">
-        <x:v>816</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="C470" s="1" t="s">
-        <x:v>817</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="D470" s="1" t="s">
         <x:v>14</x:v>
@@ -16060,10 +16015,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B471" s="1" t="s">
-        <x:v>818</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="C471" s="1" t="s">
-        <x:v>819</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="D471" s="1" t="s">
         <x:v>14</x:v>
@@ -16085,10 +16040,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B472" s="1" t="s">
-        <x:v>820</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="C472" s="1" t="s">
-        <x:v>821</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="D472" s="1" t="s">
         <x:v>14</x:v>
@@ -16114,10 +16069,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B473" s="1" t="s">
-        <x:v>822</x:v>
+        <x:v>807</x:v>
       </x:c>
       <x:c r="C473" s="1" t="s">
-        <x:v>823</x:v>
+        <x:v>808</x:v>
       </x:c>
       <x:c r="D473" s="1" t="s">
         <x:v>14</x:v>
@@ -16143,10 +16098,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B474" s="1" t="s">
-        <x:v>824</x:v>
+        <x:v>809</x:v>
       </x:c>
       <x:c r="C474" s="1" t="s">
-        <x:v>825</x:v>
+        <x:v>810</x:v>
       </x:c>
       <x:c r="D474" s="1" t="s">
         <x:v>14</x:v>
@@ -16170,10 +16125,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B475" s="1" t="s">
-        <x:v>826</x:v>
+        <x:v>811</x:v>
       </x:c>
       <x:c r="C475" s="1" t="s">
-        <x:v>827</x:v>
+        <x:v>812</x:v>
       </x:c>
       <x:c r="D475" s="1" t="s">
         <x:v>14</x:v>
@@ -16216,10 +16171,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B477" s="1" t="s">
-        <x:v>828</x:v>
+        <x:v>813</x:v>
       </x:c>
       <x:c r="C477" s="1" t="s">
-        <x:v>829</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="D477" s="1" t="s">
         <x:v>14</x:v>
@@ -16241,10 +16196,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>830</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="C478" s="1" t="s">
-        <x:v>831</x:v>
+        <x:v>816</x:v>
       </x:c>
       <x:c r="D478" s="1" t="s">
         <x:v>14</x:v>
@@ -16266,10 +16221,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>832</x:v>
+        <x:v>817</x:v>
       </x:c>
       <x:c r="C479" s="1" t="s">
-        <x:v>833</x:v>
+        <x:v>818</x:v>
       </x:c>
       <x:c r="D479" s="1" t="s">
         <x:v>14</x:v>
@@ -16280,7 +16235,7 @@
       <x:c r="F479" s="1"/>
       <x:c r="G479" s="1"/>
       <x:c r="H479" s="1" t="s">
-        <x:v>834</x:v>
+        <x:v>819</x:v>
       </x:c>
       <x:c r="I479" s="1" t="s">
         <x:v>102</x:v>
@@ -16295,10 +16250,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B480" s="1" t="s">
-        <x:v>835</x:v>
+        <x:v>820</x:v>
       </x:c>
       <x:c r="C480" s="1" t="s">
-        <x:v>836</x:v>
+        <x:v>821</x:v>
       </x:c>
       <x:c r="D480" s="1" t="s">
         <x:v>14</x:v>
@@ -16322,10 +16277,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B481" s="1" t="s">
-        <x:v>837</x:v>
+        <x:v>822</x:v>
       </x:c>
       <x:c r="C481" s="1" t="s">
-        <x:v>838</x:v>
+        <x:v>823</x:v>
       </x:c>
       <x:c r="D481" s="1" t="s">
         <x:v>14</x:v>
@@ -16351,10 +16306,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B482" s="1" t="s">
-        <x:v>839</x:v>
+        <x:v>824</x:v>
       </x:c>
       <x:c r="C482" s="1" t="s">
-        <x:v>840</x:v>
+        <x:v>825</x:v>
       </x:c>
       <x:c r="D482" s="1" t="s">
         <x:v>14</x:v>
@@ -16397,10 +16352,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B484" s="1" t="s">
-        <x:v>841</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="C484" s="1" t="s">
-        <x:v>842</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="D484" s="1" t="s">
         <x:v>14</x:v>
@@ -16422,10 +16377,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B485" s="1" t="s">
-        <x:v>843</x:v>
+        <x:v>828</x:v>
       </x:c>
       <x:c r="C485" s="1" t="s">
-        <x:v>844</x:v>
+        <x:v>829</x:v>
       </x:c>
       <x:c r="D485" s="1" t="s">
         <x:v>14</x:v>
@@ -16447,10 +16402,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B486" s="1" t="s">
-        <x:v>845</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="C486" s="1" t="s">
-        <x:v>846</x:v>
+        <x:v>831</x:v>
       </x:c>
       <x:c r="D486" s="1" t="s">
         <x:v>14</x:v>
@@ -16461,7 +16416,7 @@
       <x:c r="F486" s="1"/>
       <x:c r="G486" s="1"/>
       <x:c r="H486" s="1" t="s">
-        <x:v>847</x:v>
+        <x:v>832</x:v>
       </x:c>
       <x:c r="I486" s="1" t="s">
         <x:v>102</x:v>
@@ -16476,10 +16431,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B487" s="1" t="s">
-        <x:v>848</x:v>
+        <x:v>833</x:v>
       </x:c>
       <x:c r="C487" s="1" t="s">
-        <x:v>849</x:v>
+        <x:v>834</x:v>
       </x:c>
       <x:c r="D487" s="1" t="s">
         <x:v>14</x:v>
@@ -16503,10 +16458,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B488" s="1" t="s">
-        <x:v>850</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C488" s="1" t="s">
-        <x:v>851</x:v>
+        <x:v>836</x:v>
       </x:c>
       <x:c r="D488" s="1" t="s">
         <x:v>14</x:v>
@@ -16532,10 +16487,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B489" s="1" t="s">
-        <x:v>852</x:v>
+        <x:v>837</x:v>
       </x:c>
       <x:c r="C489" s="1" t="s">
-        <x:v>853</x:v>
+        <x:v>838</x:v>
       </x:c>
       <x:c r="D489" s="1" t="s">
         <x:v>14</x:v>
@@ -16578,10 +16533,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B491" s="1" t="s">
-        <x:v>854</x:v>
+        <x:v>839</x:v>
       </x:c>
       <x:c r="C491" s="1" t="s">
-        <x:v>855</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="D491" s="1" t="s">
         <x:v>14</x:v>
@@ -16603,10 +16558,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B492" s="1" t="s">
-        <x:v>856</x:v>
+        <x:v>841</x:v>
       </x:c>
       <x:c r="C492" s="1" t="s">
-        <x:v>857</x:v>
+        <x:v>842</x:v>
       </x:c>
       <x:c r="D492" s="1" t="s">
         <x:v>14</x:v>
@@ -16628,10 +16583,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B493" s="1" t="s">
-        <x:v>858</x:v>
+        <x:v>843</x:v>
       </x:c>
       <x:c r="C493" s="1" t="s">
-        <x:v>859</x:v>
+        <x:v>844</x:v>
       </x:c>
       <x:c r="D493" s="1" t="s">
         <x:v>14</x:v>
@@ -16642,7 +16597,7 @@
       <x:c r="F493" s="1"/>
       <x:c r="G493" s="1"/>
       <x:c r="H493" s="1" t="s">
-        <x:v>860</x:v>
+        <x:v>845</x:v>
       </x:c>
       <x:c r="I493" s="1" t="s">
         <x:v>102</x:v>
@@ -16657,10 +16612,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B494" s="1" t="s">
-        <x:v>861</x:v>
+        <x:v>846</x:v>
       </x:c>
       <x:c r="C494" s="1" t="s">
-        <x:v>862</x:v>
+        <x:v>847</x:v>
       </x:c>
       <x:c r="D494" s="1" t="s">
         <x:v>14</x:v>
@@ -16684,10 +16639,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B495" s="1" t="s">
-        <x:v>863</x:v>
+        <x:v>848</x:v>
       </x:c>
       <x:c r="C495" s="1" t="s">
-        <x:v>864</x:v>
+        <x:v>849</x:v>
       </x:c>
       <x:c r="D495" s="1" t="s">
         <x:v>14</x:v>
@@ -16713,10 +16668,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B496" s="1" t="s">
-        <x:v>865</x:v>
+        <x:v>850</x:v>
       </x:c>
       <x:c r="C496" s="1" t="s">
-        <x:v>866</x:v>
+        <x:v>851</x:v>
       </x:c>
       <x:c r="D496" s="1" t="s">
         <x:v>14</x:v>
@@ -16759,10 +16714,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B498" s="1" t="s">
-        <x:v>867</x:v>
+        <x:v>852</x:v>
       </x:c>
       <x:c r="C498" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>853</x:v>
       </x:c>
       <x:c r="D498" s="1" t="s">
         <x:v>14</x:v>
@@ -16784,10 +16739,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B499" s="1" t="s">
-        <x:v>869</x:v>
+        <x:v>854</x:v>
       </x:c>
       <x:c r="C499" s="1" t="s">
-        <x:v>870</x:v>
+        <x:v>855</x:v>
       </x:c>
       <x:c r="D499" s="1" t="s">
         <x:v>14</x:v>
@@ -16809,10 +16764,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B500" s="1" t="s">
-        <x:v>871</x:v>
+        <x:v>856</x:v>
       </x:c>
       <x:c r="C500" s="1" t="s">
-        <x:v>872</x:v>
+        <x:v>857</x:v>
       </x:c>
       <x:c r="D500" s="1" t="s">
         <x:v>14</x:v>
@@ -16823,7 +16778,7 @@
       <x:c r="F500" s="1"/>
       <x:c r="G500" s="1"/>
       <x:c r="H500" s="1" t="s">
-        <x:v>873</x:v>
+        <x:v>858</x:v>
       </x:c>
       <x:c r="I500" s="1" t="s">
         <x:v>102</x:v>
@@ -16838,10 +16793,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B501" s="1" t="s">
-        <x:v>874</x:v>
+        <x:v>859</x:v>
       </x:c>
       <x:c r="C501" s="1" t="s">
-        <x:v>875</x:v>
+        <x:v>860</x:v>
       </x:c>
       <x:c r="D501" s="1" t="s">
         <x:v>14</x:v>
@@ -16865,10 +16820,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B502" s="1" t="s">
-        <x:v>876</x:v>
+        <x:v>861</x:v>
       </x:c>
       <x:c r="C502" s="1" t="s">
-        <x:v>877</x:v>
+        <x:v>862</x:v>
       </x:c>
       <x:c r="D502" s="1" t="s">
         <x:v>14</x:v>
@@ -16894,10 +16849,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B503" s="1" t="s">
-        <x:v>878</x:v>
+        <x:v>863</x:v>
       </x:c>
       <x:c r="C503" s="1" t="s">
-        <x:v>879</x:v>
+        <x:v>864</x:v>
       </x:c>
       <x:c r="D503" s="1" t="s">
         <x:v>14</x:v>
@@ -16940,10 +16895,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B505" s="1" t="s">
-        <x:v>880</x:v>
+        <x:v>865</x:v>
       </x:c>
       <x:c r="C505" s="1" t="s">
-        <x:v>881</x:v>
+        <x:v>866</x:v>
       </x:c>
       <x:c r="D505" s="1" t="s">
         <x:v>14</x:v>
@@ -16954,7 +16909,7 @@
       </x:c>
       <x:c r="G505" s="1"/>
       <x:c r="H505" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="I505" s="1"/>
       <x:c r="J505" s="1"/>
@@ -16965,10 +16920,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B506" s="1" t="s">
-        <x:v>882</x:v>
+        <x:v>867</x:v>
       </x:c>
       <x:c r="C506" s="1" t="s">
-        <x:v>883</x:v>
+        <x:v>868</x:v>
       </x:c>
       <x:c r="D506" s="1" t="s">
         <x:v>14</x:v>
@@ -16990,10 +16945,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B507" s="1" t="s">
-        <x:v>884</x:v>
+        <x:v>869</x:v>
       </x:c>
       <x:c r="C507" s="1" t="s">
-        <x:v>885</x:v>
+        <x:v>870</x:v>
       </x:c>
       <x:c r="D507" s="1" t="s">
         <x:v>14</x:v>
@@ -17004,7 +16959,7 @@
       <x:c r="F507" s="1"/>
       <x:c r="G507" s="1"/>
       <x:c r="H507" s="1" t="s">
-        <x:v>886</x:v>
+        <x:v>871</x:v>
       </x:c>
       <x:c r="I507" s="1" t="s">
         <x:v>102</x:v>
@@ -17019,10 +16974,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B508" s="1" t="s">
-        <x:v>887</x:v>
+        <x:v>872</x:v>
       </x:c>
       <x:c r="C508" s="1" t="s">
-        <x:v>888</x:v>
+        <x:v>873</x:v>
       </x:c>
       <x:c r="D508" s="1" t="s">
         <x:v>14</x:v>
@@ -17046,10 +17001,10 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B509" s="1" t="s">
-        <x:v>889</x:v>
+        <x:v>874</x:v>
       </x:c>
       <x:c r="C509" s="1" t="s">
-        <x:v>890</x:v>
+        <x:v>875</x:v>
       </x:c>
       <x:c r="D509" s="1" t="s">
         <x:v>14</x:v>
@@ -17071,10 +17026,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B510" s="1" t="s">
-        <x:v>891</x:v>
+        <x:v>876</x:v>
       </x:c>
       <x:c r="C510" s="1" t="s">
-        <x:v>892</x:v>
+        <x:v>877</x:v>
       </x:c>
       <x:c r="D510" s="1" t="s">
         <x:v>14</x:v>
@@ -17100,10 +17055,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B511" s="1" t="s">
-        <x:v>893</x:v>
+        <x:v>878</x:v>
       </x:c>
       <x:c r="C511" s="1" t="s">
-        <x:v>894</x:v>
+        <x:v>879</x:v>
       </x:c>
       <x:c r="D511" s="1" t="s">
         <x:v>14</x:v>
@@ -17129,10 +17084,10 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B512" s="1" t="s">
-        <x:v>895</x:v>
+        <x:v>880</x:v>
       </x:c>
       <x:c r="C512" s="1" t="s">
-        <x:v>896</x:v>
+        <x:v>881</x:v>
       </x:c>
       <x:c r="D512" s="1" t="s">
         <x:v>14</x:v>
@@ -17156,10 +17111,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B513" s="1" t="s">
-        <x:v>897</x:v>
+        <x:v>882</x:v>
       </x:c>
       <x:c r="C513" s="1" t="s">
-        <x:v>898</x:v>
+        <x:v>883</x:v>
       </x:c>
       <x:c r="D513" s="1" t="s">
         <x:v>14</x:v>
@@ -17202,10 +17157,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B515" s="1" t="s">
-        <x:v>899</x:v>
+        <x:v>884</x:v>
       </x:c>
       <x:c r="C515" s="1" t="s">
-        <x:v>900</x:v>
+        <x:v>885</x:v>
       </x:c>
       <x:c r="D515" s="1" t="s">
         <x:v>14</x:v>
@@ -17216,7 +17171,7 @@
       </x:c>
       <x:c r="G515" s="1"/>
       <x:c r="H515" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="I515" s="1"/>
       <x:c r="J515" s="1"/>
@@ -17227,10 +17182,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B516" s="1" t="s">
-        <x:v>901</x:v>
+        <x:v>886</x:v>
       </x:c>
       <x:c r="C516" s="1" t="s">
-        <x:v>902</x:v>
+        <x:v>887</x:v>
       </x:c>
       <x:c r="D516" s="1" t="s">
         <x:v>14</x:v>
@@ -17252,10 +17207,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B517" s="1" t="s">
-        <x:v>903</x:v>
+        <x:v>888</x:v>
       </x:c>
       <x:c r="C517" s="1" t="s">
-        <x:v>904</x:v>
+        <x:v>889</x:v>
       </x:c>
       <x:c r="D517" s="1" t="s">
         <x:v>14</x:v>
@@ -17266,7 +17221,7 @@
       <x:c r="F517" s="1"/>
       <x:c r="G517" s="1"/>
       <x:c r="H517" s="1" t="s">
-        <x:v>905</x:v>
+        <x:v>890</x:v>
       </x:c>
       <x:c r="I517" s="1" t="s">
         <x:v>102</x:v>
@@ -17281,10 +17236,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B518" s="1" t="s">
-        <x:v>906</x:v>
+        <x:v>891</x:v>
       </x:c>
       <x:c r="C518" s="1" t="s">
-        <x:v>907</x:v>
+        <x:v>892</x:v>
       </x:c>
       <x:c r="D518" s="1" t="s">
         <x:v>14</x:v>
@@ -17308,10 +17263,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B519" s="1" t="s">
-        <x:v>908</x:v>
+        <x:v>893</x:v>
       </x:c>
       <x:c r="C519" s="1" t="s">
-        <x:v>909</x:v>
+        <x:v>894</x:v>
       </x:c>
       <x:c r="D519" s="1" t="s">
         <x:v>14</x:v>
@@ -17337,10 +17292,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B520" s="1" t="s">
-        <x:v>910</x:v>
+        <x:v>895</x:v>
       </x:c>
       <x:c r="C520" s="1" t="s">
-        <x:v>911</x:v>
+        <x:v>896</x:v>
       </x:c>
       <x:c r="D520" s="1" t="s">
         <x:v>14</x:v>
@@ -17383,10 +17338,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B522" s="1" t="s">
-        <x:v>912</x:v>
+        <x:v>897</x:v>
       </x:c>
       <x:c r="C522" s="1" t="s">
-        <x:v>913</x:v>
+        <x:v>898</x:v>
       </x:c>
       <x:c r="D522" s="1" t="s">
         <x:v>14</x:v>
@@ -17397,7 +17352,7 @@
       </x:c>
       <x:c r="G522" s="1"/>
       <x:c r="H522" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="I522" s="1"/>
       <x:c r="J522" s="1"/>
@@ -17408,10 +17363,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B523" s="1" t="s">
-        <x:v>914</x:v>
+        <x:v>899</x:v>
       </x:c>
       <x:c r="C523" s="1" t="s">
-        <x:v>915</x:v>
+        <x:v>900</x:v>
       </x:c>
       <x:c r="D523" s="1" t="s">
         <x:v>14</x:v>
@@ -17433,10 +17388,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B524" s="1" t="s">
-        <x:v>916</x:v>
+        <x:v>901</x:v>
       </x:c>
       <x:c r="C524" s="1" t="s">
-        <x:v>917</x:v>
+        <x:v>902</x:v>
       </x:c>
       <x:c r="D524" s="1" t="s">
         <x:v>14</x:v>
@@ -17447,7 +17402,7 @@
       <x:c r="F524" s="1"/>
       <x:c r="G524" s="1"/>
       <x:c r="H524" s="1" t="s">
-        <x:v>918</x:v>
+        <x:v>903</x:v>
       </x:c>
       <x:c r="I524" s="1" t="s">
         <x:v>102</x:v>
@@ -17462,10 +17417,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B525" s="1" t="s">
-        <x:v>919</x:v>
+        <x:v>904</x:v>
       </x:c>
       <x:c r="C525" s="1" t="s">
-        <x:v>920</x:v>
+        <x:v>905</x:v>
       </x:c>
       <x:c r="D525" s="1" t="s">
         <x:v>14</x:v>
@@ -17489,10 +17444,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B526" s="1" t="s">
-        <x:v>921</x:v>
+        <x:v>906</x:v>
       </x:c>
       <x:c r="C526" s="1" t="s">
-        <x:v>922</x:v>
+        <x:v>907</x:v>
       </x:c>
       <x:c r="D526" s="1" t="s">
         <x:v>14</x:v>
@@ -17518,10 +17473,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B527" s="1" t="s">
-        <x:v>923</x:v>
+        <x:v>908</x:v>
       </x:c>
       <x:c r="C527" s="1" t="s">
-        <x:v>924</x:v>
+        <x:v>909</x:v>
       </x:c>
       <x:c r="D527" s="1" t="s">
         <x:v>14</x:v>
@@ -17564,10 +17519,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B529" s="1" t="s">
-        <x:v>925</x:v>
+        <x:v>910</x:v>
       </x:c>
       <x:c r="C529" s="1" t="s">
-        <x:v>926</x:v>
+        <x:v>911</x:v>
       </x:c>
       <x:c r="D529" s="1" t="s">
         <x:v>14</x:v>
@@ -17578,7 +17533,7 @@
       </x:c>
       <x:c r="G529" s="1"/>
       <x:c r="H529" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="I529" s="1"/>
       <x:c r="J529" s="1"/>
@@ -17589,10 +17544,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B530" s="1" t="s">
-        <x:v>927</x:v>
+        <x:v>912</x:v>
       </x:c>
       <x:c r="C530" s="1" t="s">
-        <x:v>928</x:v>
+        <x:v>913</x:v>
       </x:c>
       <x:c r="D530" s="1" t="s">
         <x:v>14</x:v>
@@ -17614,10 +17569,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B531" s="1" t="s">
-        <x:v>929</x:v>
+        <x:v>914</x:v>
       </x:c>
       <x:c r="C531" s="1" t="s">
-        <x:v>930</x:v>
+        <x:v>915</x:v>
       </x:c>
       <x:c r="D531" s="1" t="s">
         <x:v>14</x:v>
@@ -17628,7 +17583,7 @@
       <x:c r="F531" s="1"/>
       <x:c r="G531" s="1"/>
       <x:c r="H531" s="1" t="s">
-        <x:v>931</x:v>
+        <x:v>916</x:v>
       </x:c>
       <x:c r="I531" s="1" t="s">
         <x:v>102</x:v>
@@ -17643,10 +17598,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B532" s="1" t="s">
-        <x:v>932</x:v>
+        <x:v>917</x:v>
       </x:c>
       <x:c r="C532" s="1" t="s">
-        <x:v>933</x:v>
+        <x:v>918</x:v>
       </x:c>
       <x:c r="D532" s="1" t="s">
         <x:v>14</x:v>
@@ -17670,10 +17625,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B533" s="1" t="s">
-        <x:v>934</x:v>
+        <x:v>919</x:v>
       </x:c>
       <x:c r="C533" s="1" t="s">
-        <x:v>935</x:v>
+        <x:v>920</x:v>
       </x:c>
       <x:c r="D533" s="1" t="s">
         <x:v>14</x:v>
@@ -17699,10 +17654,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B534" s="1" t="s">
-        <x:v>936</x:v>
+        <x:v>921</x:v>
       </x:c>
       <x:c r="C534" s="1" t="s">
-        <x:v>937</x:v>
+        <x:v>922</x:v>
       </x:c>
       <x:c r="D534" s="1" t="s">
         <x:v>14</x:v>
@@ -17745,10 +17700,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B536" s="1" t="s">
-        <x:v>938</x:v>
+        <x:v>923</x:v>
       </x:c>
       <x:c r="C536" s="1" t="s">
-        <x:v>939</x:v>
+        <x:v>924</x:v>
       </x:c>
       <x:c r="D536" s="1" t="s">
         <x:v>14</x:v>
@@ -17759,7 +17714,7 @@
       </x:c>
       <x:c r="G536" s="1"/>
       <x:c r="H536" s="1" t="s">
-        <x:v>517</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="I536" s="1"/>
       <x:c r="J536" s="1"/>
@@ -17770,10 +17725,10 @@
         <x:v>93</x:v>
       </x:c>
       <x:c r="B537" s="1" t="s">
-        <x:v>940</x:v>
+        <x:v>925</x:v>
       </x:c>
       <x:c r="C537" s="1" t="s">
-        <x:v>941</x:v>
+        <x:v>926</x:v>
       </x:c>
       <x:c r="D537" s="1" t="s">
         <x:v>14</x:v>
@@ -17795,10 +17750,10 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B538" s="1" t="s">
-        <x:v>942</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="C538" s="1" t="s">
-        <x:v>943</x:v>
+        <x:v>928</x:v>
       </x:c>
       <x:c r="D538" s="1" t="s">
         <x:v>14</x:v>
@@ -17809,7 +17764,7 @@
       <x:c r="F538" s="1"/>
       <x:c r="G538" s="1"/>
       <x:c r="H538" s="1" t="s">
-        <x:v>944</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="I538" s="1" t="s">
         <x:v>102</x:v>
@@ -17824,10 +17779,10 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="B539" s="1" t="s">
-        <x:v>945</x:v>
+        <x:v>930</x:v>
       </x:c>
       <x:c r="C539" s="1" t="s">
-        <x:v>946</x:v>
+        <x:v>931</x:v>
       </x:c>
       <x:c r="D539" s="1" t="s">
         <x:v>14</x:v>
@@ -17851,10 +17806,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B540" s="1" t="s">
-        <x:v>947</x:v>
+        <x:v>932</x:v>
       </x:c>
       <x:c r="C540" s="1" t="s">
-        <x:v>948</x:v>
+        <x:v>933</x:v>
       </x:c>
       <x:c r="D540" s="1" t="s">
         <x:v>14</x:v>
@@ -17880,10 +17835,10 @@
         <x:v>211</x:v>
       </x:c>
       <x:c r="B541" s="1" t="s">
-        <x:v>949</x:v>
+        <x:v>934</x:v>
       </x:c>
       <x:c r="C541" s="1" t="s">
-        <x:v>950</x:v>
+        <x:v>935</x:v>
       </x:c>
       <x:c r="D541" s="1" t="s">
         <x:v>14</x:v>
@@ -18008,10 +17963,10 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B549" s="1" t="s">
-        <x:v>951</x:v>
+        <x:v>936</x:v>
       </x:c>
       <x:c r="C549" s="1" t="s">
-        <x:v>952</x:v>
+        <x:v>937</x:v>
       </x:c>
       <x:c r="D549" s="1" t="s">
         <x:v>14</x:v>
@@ -18031,16 +17986,16 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B550" s="1" t="s">
-        <x:v>953</x:v>
+        <x:v>938</x:v>
       </x:c>
       <x:c r="C550" s="1" t="s">
-        <x:v>954</x:v>
+        <x:v>939</x:v>
       </x:c>
       <x:c r="D550" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="E550" s="1" t="s">
-        <x:v>955</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="F550" s="1"/>
       <x:c r="G550" s="1"/>
@@ -18054,16 +18009,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B551" s="1" t="s">
-        <x:v>956</x:v>
+        <x:v>941</x:v>
       </x:c>
       <x:c r="C551" s="1" t="s">
-        <x:v>957</x:v>
+        <x:v>942</x:v>
       </x:c>
       <x:c r="D551" s="1" t="s">
-        <x:v>958</x:v>
+        <x:v>943</x:v>
       </x:c>
       <x:c r="E551" s="1" t="s">
-        <x:v>959</x:v>
+        <x:v>944</x:v>
       </x:c>
       <x:c r="F551" s="1" t="s">
         <x:v>76</x:v>
@@ -18079,16 +18034,16 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B552" s="1" t="s">
-        <x:v>960</x:v>
+        <x:v>945</x:v>
       </x:c>
       <x:c r="C552" s="1" t="s">
-        <x:v>961</x:v>
+        <x:v>946</x:v>
       </x:c>
       <x:c r="D552" s="1" t="s">
-        <x:v>958</x:v>
+        <x:v>943</x:v>
       </x:c>
       <x:c r="E552" s="1" t="s">
-        <x:v>962</x:v>
+        <x:v>947</x:v>
       </x:c>
       <x:c r="F552" s="1" t="s">
         <x:v>76</x:v>
@@ -18237,7 +18192,7 @@
   <x:sheetData>
     <x:row r="1" ht="1.75" customHeight="1">
       <x:c r="A1" s="4" t="s">
-        <x:v>963</x:v>
+        <x:v>948</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
         <x:v>1</x:v>
@@ -18249,7 +18204,7 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E1" s="4" t="s">
-        <x:v>964</x:v>
+        <x:v>949</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -18257,10 +18212,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>965</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>966</x:v>
+        <x:v>951</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
       <x:c r="E2" s="1"/>
@@ -18270,10 +18225,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>967</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>968</x:v>
+        <x:v>953</x:v>
       </x:c>
       <x:c r="D3" s="1"/>
       <x:c r="E3" s="1"/>
@@ -18283,10 +18238,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>969</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>970</x:v>
+        <x:v>955</x:v>
       </x:c>
       <x:c r="D4" s="1"/>
       <x:c r="E4" s="1"/>
@@ -18296,10 +18251,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>971</x:v>
+        <x:v>956</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>972</x:v>
+        <x:v>957</x:v>
       </x:c>
       <x:c r="D5" s="1"/>
       <x:c r="E5" s="1"/>
@@ -18309,10 +18264,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>973</x:v>
+        <x:v>958</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>974</x:v>
+        <x:v>959</x:v>
       </x:c>
       <x:c r="D6" s="1"/>
       <x:c r="E6" s="1"/>
@@ -18322,10 +18277,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>975</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>976</x:v>
+        <x:v>961</x:v>
       </x:c>
       <x:c r="D7" s="1"/>
       <x:c r="E7" s="1"/>
@@ -18335,10 +18290,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>977</x:v>
+        <x:v>962</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>978</x:v>
+        <x:v>963</x:v>
       </x:c>
       <x:c r="D8" s="1"/>
       <x:c r="E8" s="1"/>
@@ -18348,10 +18303,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>979</x:v>
+        <x:v>964</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>980</x:v>
+        <x:v>965</x:v>
       </x:c>
       <x:c r="D9" s="1"/>
       <x:c r="E9" s="1"/>
@@ -18361,13 +18316,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>981</x:v>
+        <x:v>966</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>982</x:v>
+        <x:v>967</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>979</x:v>
+        <x:v>964</x:v>
       </x:c>
       <x:c r="E10" s="1"/>
     </x:row>
@@ -18376,13 +18331,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>983</x:v>
+        <x:v>968</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>984</x:v>
+        <x:v>969</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>977</x:v>
+        <x:v>962</x:v>
       </x:c>
       <x:c r="E11" s="1"/>
     </x:row>
@@ -18391,13 +18346,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>985</x:v>
+        <x:v>970</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>986</x:v>
+        <x:v>971</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>973</x:v>
+        <x:v>958</x:v>
       </x:c>
       <x:c r="E12" s="1"/>
     </x:row>
@@ -18406,13 +18361,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>987</x:v>
+        <x:v>972</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>988</x:v>
+        <x:v>973</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>971</x:v>
+        <x:v>956</x:v>
       </x:c>
       <x:c r="E13" s="1"/>
     </x:row>
@@ -18421,13 +18376,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>989</x:v>
+        <x:v>974</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>990</x:v>
+        <x:v>975</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>967</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="E14" s="1"/>
     </x:row>
@@ -18436,13 +18391,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>991</x:v>
+        <x:v>976</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>992</x:v>
+        <x:v>977</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>975</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="E15" s="1"/>
     </x:row>
@@ -18451,13 +18406,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>993</x:v>
+        <x:v>978</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>994</x:v>
+        <x:v>979</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>971</x:v>
+        <x:v>956</x:v>
       </x:c>
       <x:c r="E16" s="1"/>
     </x:row>
@@ -18466,13 +18421,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>995</x:v>
+        <x:v>980</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>996</x:v>
+        <x:v>981</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>965</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="E17" s="1"/>
     </x:row>
@@ -18481,13 +18436,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>997</x:v>
+        <x:v>982</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>998</x:v>
+        <x:v>983</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>965</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="E18" s="1"/>
     </x:row>
@@ -18496,13 +18451,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>999</x:v>
+        <x:v>984</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>1000</x:v>
+        <x:v>985</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>965</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="E19" s="1"/>
     </x:row>
@@ -18511,13 +18466,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>1001</x:v>
+        <x:v>986</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>1002</x:v>
+        <x:v>987</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>965</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="E20" s="1"/>
     </x:row>
@@ -18526,13 +18481,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>1003</x:v>
+        <x:v>988</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>1004</x:v>
+        <x:v>989</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>965</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="E21" s="1"/>
     </x:row>
@@ -18541,13 +18496,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>1005</x:v>
+        <x:v>990</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>1006</x:v>
+        <x:v>991</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>965</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="E22" s="1"/>
     </x:row>
@@ -18556,13 +18511,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>1007</x:v>
+        <x:v>992</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>1008</x:v>
+        <x:v>993</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>965</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="E23" s="1"/>
     </x:row>
@@ -18571,13 +18526,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>1009</x:v>
+        <x:v>994</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>1010</x:v>
+        <x:v>995</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>965</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="E24" s="1"/>
     </x:row>
@@ -18586,13 +18541,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>1011</x:v>
+        <x:v>996</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>1012</x:v>
+        <x:v>997</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>965</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="E25" s="1"/>
     </x:row>
@@ -18601,13 +18556,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>1013</x:v>
+        <x:v>998</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>1014</x:v>
+        <x:v>999</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>973</x:v>
+        <x:v>958</x:v>
       </x:c>
       <x:c r="E26" s="1"/>
     </x:row>
@@ -18616,13 +18571,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>1015</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>1016</x:v>
+        <x:v>1001</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>979</x:v>
+        <x:v>964</x:v>
       </x:c>
       <x:c r="E27" s="1"/>
     </x:row>
@@ -18631,13 +18586,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>1017</x:v>
+        <x:v>1002</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>1018</x:v>
+        <x:v>1003</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>967</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="E28" s="1"/>
     </x:row>
@@ -18646,13 +18601,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>1019</x:v>
+        <x:v>1004</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>1020</x:v>
+        <x:v>1005</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>969</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="E29" s="1"/>
     </x:row>
@@ -18661,13 +18616,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>1021</x:v>
+        <x:v>1006</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>1022</x:v>
+        <x:v>1007</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>969</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="E30" s="1"/>
     </x:row>
@@ -18676,13 +18631,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>1023</x:v>
+        <x:v>1008</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>1024</x:v>
+        <x:v>1009</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>975</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="E31" s="1"/>
     </x:row>
@@ -18691,13 +18646,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>1025</x:v>
+        <x:v>1010</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>1026</x:v>
+        <x:v>1011</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>967</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="E32" s="1"/>
     </x:row>
@@ -18706,13 +18661,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>1027</x:v>
+        <x:v>1012</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>1028</x:v>
+        <x:v>1013</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>967</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="E33" s="1"/>
     </x:row>
@@ -18721,13 +18676,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>1029</x:v>
+        <x:v>1014</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>1030</x:v>
+        <x:v>1015</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>969</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="E34" s="1"/>
     </x:row>
@@ -18736,13 +18691,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>1031</x:v>
+        <x:v>1016</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>1032</x:v>
+        <x:v>1017</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>969</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="E35" s="1"/>
     </x:row>
@@ -18751,13 +18706,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>1033</x:v>
+        <x:v>1018</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>1034</x:v>
+        <x:v>1019</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>969</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="E36" s="1"/>
     </x:row>
@@ -18766,13 +18721,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>1035</x:v>
+        <x:v>1020</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>1036</x:v>
+        <x:v>1021</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>969</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="E37" s="1"/>
     </x:row>
@@ -18781,13 +18736,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>1037</x:v>
+        <x:v>1022</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>1038</x:v>
+        <x:v>1023</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>971</x:v>
+        <x:v>956</x:v>
       </x:c>
       <x:c r="E38" s="1"/>
     </x:row>
@@ -18796,13 +18751,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>1039</x:v>
+        <x:v>1024</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>1040</x:v>
+        <x:v>1025</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>977</x:v>
+        <x:v>962</x:v>
       </x:c>
       <x:c r="E39" s="1"/>
     </x:row>
@@ -18811,13 +18766,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>1041</x:v>
+        <x:v>1026</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>1042</x:v>
+        <x:v>1027</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>967</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="E40" s="1"/>
     </x:row>
@@ -18826,13 +18781,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>1043</x:v>
+        <x:v>1028</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>1044</x:v>
+        <x:v>1029</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>977</x:v>
+        <x:v>962</x:v>
       </x:c>
       <x:c r="E41" s="1"/>
     </x:row>
@@ -18841,13 +18796,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>1045</x:v>
+        <x:v>1030</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>1046</x:v>
+        <x:v>1031</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>969</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="E42" s="1"/>
     </x:row>
@@ -18856,13 +18811,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>1047</x:v>
+        <x:v>1032</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>1048</x:v>
+        <x:v>1033</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>969</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="E43" s="1"/>
     </x:row>
@@ -18871,13 +18826,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>1049</x:v>
+        <x:v>1034</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>1050</x:v>
+        <x:v>1035</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>967</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="E44" s="1"/>
     </x:row>
@@ -18886,13 +18841,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>1051</x:v>
+        <x:v>1036</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>1052</x:v>
+        <x:v>1037</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>967</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="E45" s="1"/>
     </x:row>
@@ -18901,13 +18856,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>1053</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>1054</x:v>
+        <x:v>1039</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>973</x:v>
+        <x:v>958</x:v>
       </x:c>
       <x:c r="E46" s="1"/>
     </x:row>
@@ -18916,13 +18871,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>1055</x:v>
+        <x:v>1040</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>1056</x:v>
+        <x:v>1041</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>969</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="E47" s="1"/>
     </x:row>
@@ -18931,13 +18886,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>1057</x:v>
+        <x:v>1042</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>1058</x:v>
+        <x:v>1043</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>973</x:v>
+        <x:v>958</x:v>
       </x:c>
       <x:c r="E48" s="1"/>
     </x:row>
@@ -18946,13 +18901,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>1059</x:v>
+        <x:v>1044</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>1060</x:v>
+        <x:v>1045</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>969</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="E49" s="1"/>
     </x:row>
@@ -18961,13 +18916,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>1061</x:v>
+        <x:v>1046</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>1062</x:v>
+        <x:v>1047</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>977</x:v>
+        <x:v>962</x:v>
       </x:c>
       <x:c r="E50" s="1"/>
     </x:row>
@@ -18976,13 +18931,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>1063</x:v>
+        <x:v>1048</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>1064</x:v>
+        <x:v>1049</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>975</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="E51" s="1"/>
     </x:row>
@@ -18991,13 +18946,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>1065</x:v>
+        <x:v>1050</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>1066</x:v>
+        <x:v>1051</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>971</x:v>
+        <x:v>956</x:v>
       </x:c>
       <x:c r="E52" s="1"/>
     </x:row>
@@ -19006,13 +18961,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>1067</x:v>
+        <x:v>1052</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>1068</x:v>
+        <x:v>1053</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>967</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="E53" s="1"/>
     </x:row>
@@ -19021,13 +18976,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>1069</x:v>
+        <x:v>1054</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>1070</x:v>
+        <x:v>1055</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>971</x:v>
+        <x:v>956</x:v>
       </x:c>
       <x:c r="E54" s="1"/>
     </x:row>
@@ -19036,13 +18991,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>1071</x:v>
+        <x:v>1056</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>1072</x:v>
+        <x:v>1057</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>967</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="E55" s="1"/>
     </x:row>
@@ -19051,13 +19006,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>1073</x:v>
+        <x:v>1058</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>1074</x:v>
+        <x:v>1059</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>969</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="E56" s="1"/>
     </x:row>
@@ -19066,13 +19021,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>1075</x:v>
+        <x:v>1060</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>1076</x:v>
+        <x:v>1061</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>973</x:v>
+        <x:v>958</x:v>
       </x:c>
       <x:c r="E57" s="1"/>
     </x:row>
@@ -19081,13 +19036,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>1077</x:v>
+        <x:v>1062</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>1078</x:v>
+        <x:v>1063</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>971</x:v>
+        <x:v>956</x:v>
       </x:c>
       <x:c r="E58" s="1"/>
     </x:row>
@@ -19096,13 +19051,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>1079</x:v>
+        <x:v>1064</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>1080</x:v>
+        <x:v>1065</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>965</x:v>
+        <x:v>950</x:v>
       </x:c>
       <x:c r="E59" s="1"/>
     </x:row>
@@ -19111,13 +19066,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>1081</x:v>
+        <x:v>1066</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>1082</x:v>
+        <x:v>1067</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>973</x:v>
+        <x:v>958</x:v>
       </x:c>
       <x:c r="E60" s="1"/>
     </x:row>
@@ -19126,13 +19081,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>1083</x:v>
+        <x:v>1068</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>1084</x:v>
+        <x:v>1069</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>971</x:v>
+        <x:v>956</x:v>
       </x:c>
       <x:c r="E61" s="1"/>
     </x:row>
@@ -19141,13 +19096,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>1085</x:v>
+        <x:v>1070</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>1086</x:v>
+        <x:v>1071</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>979</x:v>
+        <x:v>964</x:v>
       </x:c>
       <x:c r="E62" s="1"/>
     </x:row>
@@ -19156,13 +19111,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>1087</x:v>
+        <x:v>1072</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>1088</x:v>
+        <x:v>1073</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>977</x:v>
+        <x:v>962</x:v>
       </x:c>
       <x:c r="E63" s="1"/>
     </x:row>
@@ -19171,13 +19126,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>1089</x:v>
+        <x:v>1074</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>1090</x:v>
+        <x:v>1075</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>979</x:v>
+        <x:v>964</x:v>
       </x:c>
       <x:c r="E64" s="1"/>
     </x:row>
@@ -19186,13 +19141,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>1091</x:v>
+        <x:v>1076</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>1092</x:v>
+        <x:v>1077</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>977</x:v>
+        <x:v>962</x:v>
       </x:c>
       <x:c r="E65" s="1"/>
     </x:row>
@@ -19201,13 +19156,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>1093</x:v>
+        <x:v>1078</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>1094</x:v>
+        <x:v>1079</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>969</x:v>
+        <x:v>954</x:v>
       </x:c>
       <x:c r="E66" s="1"/>
     </x:row>
@@ -19216,13 +19171,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>1095</x:v>
+        <x:v>1080</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>1096</x:v>
+        <x:v>1081</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>973</x:v>
+        <x:v>958</x:v>
       </x:c>
       <x:c r="E67" s="1"/>
     </x:row>
@@ -19231,13 +19186,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>1097</x:v>
+        <x:v>1082</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>1098</x:v>
+        <x:v>1083</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>977</x:v>
+        <x:v>962</x:v>
       </x:c>
       <x:c r="E68" s="1"/>
     </x:row>
@@ -19246,13 +19201,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>1099</x:v>
+        <x:v>1084</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>1100</x:v>
+        <x:v>1085</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>975</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="E69" s="1"/>
     </x:row>
@@ -19261,13 +19216,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>1101</x:v>
+        <x:v>1086</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>1102</x:v>
+        <x:v>1087</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>967</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="E70" s="1"/>
     </x:row>
@@ -19276,13 +19231,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>1103</x:v>
+        <x:v>1088</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>1104</x:v>
+        <x:v>1089</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>967</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="E71" s="1"/>
     </x:row>
@@ -19291,13 +19246,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>1105</x:v>
+        <x:v>1090</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>1106</x:v>
+        <x:v>1091</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>967</x:v>
+        <x:v>952</x:v>
       </x:c>
       <x:c r="E72" s="1"/>
     </x:row>
@@ -19306,13 +19261,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>1107</x:v>
+        <x:v>1092</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>1108</x:v>
+        <x:v>1093</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>975</x:v>
+        <x:v>960</x:v>
       </x:c>
       <x:c r="E73" s="1"/>
     </x:row>
@@ -19321,13 +19276,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>1109</x:v>
+        <x:v>1094</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>1110</x:v>
+        <x:v>1095</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>971</x:v>
+        <x:v>956</x:v>
       </x:c>
       <x:c r="E74" s="1"/>
     </x:row>
@@ -19336,14 +19291,14 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>1111</x:v>
+        <x:v>1096</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>1112</x:v>
+        <x:v>1097</x:v>
       </x:c>
       <x:c r="D75" s="1"/>
       <x:c r="E75" s="1" t="s">
-        <x:v>1113</x:v>
+        <x:v>1098</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="1.75" customHeight="1">
@@ -19351,14 +19306,14 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>1114</x:v>
+        <x:v>1099</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>1115</x:v>
+        <x:v>1100</x:v>
       </x:c>
       <x:c r="D76" s="1"/>
       <x:c r="E76" s="1" t="s">
-        <x:v>1113</x:v>
+        <x:v>1098</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="1.75" customHeight="1">
@@ -19366,14 +19321,14 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>1116</x:v>
+        <x:v>1101</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>1117</x:v>
+        <x:v>1102</x:v>
       </x:c>
       <x:c r="D77" s="1"/>
       <x:c r="E77" s="1" t="s">
-        <x:v>1118</x:v>
+        <x:v>1103</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="1.75" customHeight="1">
@@ -19381,14 +19336,14 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>1119</x:v>
+        <x:v>1104</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>1120</x:v>
+        <x:v>1105</x:v>
       </x:c>
       <x:c r="D78" s="1"/>
       <x:c r="E78" s="1" t="s">
-        <x:v>1113</x:v>
+        <x:v>1098</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -19396,116 +19351,116 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>1121</x:v>
+        <x:v>1106</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>1122</x:v>
+        <x:v>1107</x:v>
       </x:c>
       <x:c r="D79" s="1"/>
       <x:c r="E79" s="1" t="s">
-        <x:v>1113</x:v>
+        <x:v>1098</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="1" t="s">
-        <x:v>1123</x:v>
+        <x:v>1108</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>1124</x:v>
+        <x:v>1109</x:v>
       </x:c>
       <x:c r="D80" s="1"/>
       <x:c r="E80" s="1"/>
     </x:row>
     <x:row r="81" ht="1.75" customHeight="1">
       <x:c r="A81" s="1" t="s">
-        <x:v>1123</x:v>
+        <x:v>1108</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>1125</x:v>
+        <x:v>1110</x:v>
       </x:c>
       <x:c r="D81" s="1"/>
       <x:c r="E81" s="1"/>
     </x:row>
     <x:row r="82" ht="1.75" customHeight="1">
       <x:c r="A82" s="1" t="s">
-        <x:v>1126</x:v>
+        <x:v>1111</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>1127</x:v>
+        <x:v>1112</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>1128</x:v>
+        <x:v>1113</x:v>
       </x:c>
       <x:c r="D82" s="1"/>
       <x:c r="E82" s="1"/>
     </x:row>
     <x:row r="83" ht="1.75" customHeight="1">
       <x:c r="A83" s="1" t="s">
-        <x:v>1126</x:v>
+        <x:v>1111</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>1129</x:v>
+        <x:v>1114</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>1130</x:v>
+        <x:v>1115</x:v>
       </x:c>
       <x:c r="D83" s="1"/>
       <x:c r="E83" s="1"/>
     </x:row>
     <x:row r="84" ht="1.75" customHeight="1">
       <x:c r="A84" s="1" t="s">
-        <x:v>1126</x:v>
+        <x:v>1111</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>1131</x:v>
+        <x:v>1116</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>1132</x:v>
+        <x:v>1117</x:v>
       </x:c>
       <x:c r="D84" s="1"/>
       <x:c r="E84" s="1"/>
     </x:row>
     <x:row r="85" ht="1.75" customHeight="1">
       <x:c r="A85" s="1" t="s">
-        <x:v>1133</x:v>
+        <x:v>1118</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>1134</x:v>
+        <x:v>1119</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>1135</x:v>
+        <x:v>1120</x:v>
       </x:c>
       <x:c r="D85" s="1"/>
       <x:c r="E85" s="1"/>
     </x:row>
     <x:row r="86" ht="1.75" customHeight="1">
       <x:c r="A86" s="1" t="s">
-        <x:v>1133</x:v>
+        <x:v>1118</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>1136</x:v>
+        <x:v>1121</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>1137</x:v>
+        <x:v>1122</x:v>
       </x:c>
       <x:c r="D86" s="1"/>
       <x:c r="E86" s="1"/>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="1" t="s">
-        <x:v>1133</x:v>
+        <x:v>1118</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>1138</x:v>
+        <x:v>1123</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>1139</x:v>
+        <x:v>1124</x:v>
       </x:c>
       <x:c r="D87" s="1"/>
       <x:c r="E87" s="1"/>
@@ -19529,14 +19484,14 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>1140</x:v>
+        <x:v>1125</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>1141</x:v>
+        <x:v>1126</x:v>
       </x:c>
       <x:c r="D90" s="1"/>
       <x:c r="E90" s="1" t="s">
-        <x:v>1118</x:v>
+        <x:v>1103</x:v>
       </x:c>
     </x:row>
     <x:row r="91">
@@ -19544,14 +19499,14 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>1142</x:v>
+        <x:v>1127</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>1143</x:v>
+        <x:v>1128</x:v>
       </x:c>
       <x:c r="D91" s="1"/>
       <x:c r="E91" s="1" t="s">
-        <x:v>1118</x:v>
+        <x:v>1103</x:v>
       </x:c>
     </x:row>
     <x:row r="92">
@@ -19559,14 +19514,14 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>1144</x:v>
+        <x:v>1129</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>1145</x:v>
+        <x:v>1130</x:v>
       </x:c>
       <x:c r="D92" s="1"/>
       <x:c r="E92" s="1" t="s">
-        <x:v>1118</x:v>
+        <x:v>1103</x:v>
       </x:c>
     </x:row>
     <x:row r="93">
@@ -19574,14 +19529,14 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>1146</x:v>
+        <x:v>1131</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>1147</x:v>
+        <x:v>1132</x:v>
       </x:c>
       <x:c r="D93" s="1"/>
       <x:c r="E93" s="1" t="s">
-        <x:v>1118</x:v>
+        <x:v>1103</x:v>
       </x:c>
     </x:row>
     <x:row r="94">
@@ -19589,38 +19544,38 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>1148</x:v>
+        <x:v>1133</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>1149</x:v>
+        <x:v>1134</x:v>
       </x:c>
       <x:c r="D94" s="1"/>
       <x:c r="E94" s="1" t="s">
-        <x:v>1118</x:v>
+        <x:v>1103</x:v>
       </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="1" t="s">
-        <x:v>1150</x:v>
+        <x:v>1135</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>1113</x:v>
+        <x:v>1098</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>1151</x:v>
+        <x:v>1136</x:v>
       </x:c>
       <x:c r="D95" s="1"/>
       <x:c r="E95" s="1"/>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="1" t="s">
-        <x:v>1150</x:v>
+        <x:v>1135</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>1118</x:v>
+        <x:v>1103</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>1152</x:v>
+        <x:v>1137</x:v>
       </x:c>
       <x:c r="D96" s="1"/>
       <x:c r="E96" s="1"/>
@@ -19640,18 +19595,18 @@
   <x:sheetData>
     <x:row r="1" ht="1.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>1153</x:v>
+        <x:v>1138</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>1154</x:v>
+        <x:v>1139</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="5.150000095367432" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>1155</x:v>
+        <x:v>1140</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>1156</x:v>
+        <x:v>1141</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -19670,90 +19625,90 @@
   <x:sheetData>
     <x:row r="1" ht="20" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>1157</x:v>
+        <x:v>1142</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>1158</x:v>
+        <x:v>1143</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>1159</x:v>
+        <x:v>1144</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="20" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>1160</x:v>
+        <x:v>1145</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>1161</x:v>
+        <x:v>1146</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>1162</x:v>
+        <x:v>1147</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="20" customHeight="1">
       <x:c r="A3" s="1" t="s">
-        <x:v>1163</x:v>
+        <x:v>1148</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>1164</x:v>
+        <x:v>1149</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>1165</x:v>
+        <x:v>1150</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="20" customHeight="1">
       <x:c r="A4" s="1" t="s">
-        <x:v>1166</x:v>
+        <x:v>1151</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>1167</x:v>
+        <x:v>1152</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>1168</x:v>
+        <x:v>1153</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="20" customHeight="1">
       <x:c r="A5" s="1" t="s">
-        <x:v>1169</x:v>
+        <x:v>1154</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>1170</x:v>
+        <x:v>1155</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>1171</x:v>
+        <x:v>1156</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="20" customHeight="1">
       <x:c r="A6" s="1" t="s">
-        <x:v>1172</x:v>
+        <x:v>1157</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>1173</x:v>
+        <x:v>1158</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>1174</x:v>
+        <x:v>1159</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="20" customHeight="1">
       <x:c r="A7" s="1" t="s">
-        <x:v>1175</x:v>
+        <x:v>1160</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>1176</x:v>
+        <x:v>1161</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>1177</x:v>
+        <x:v>1162</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="20" customHeight="1">
       <x:c r="A8" s="1" t="s">
-        <x:v>1178</x:v>
+        <x:v>1163</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>1179</x:v>
+        <x:v>1164</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>1180</x:v>
+        <x:v>1165</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="20" customHeight="1">
@@ -19799,257 +19754,257 @@
   <x:sheetData>
     <x:row r="1" ht="1.75" customHeight="1">
       <x:c r="A1" s="2" t="s">
-        <x:v>1181</x:v>
+        <x:v>1166</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>1182</x:v>
+        <x:v>1167</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>1183</x:v>
+        <x:v>1168</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>1184</x:v>
+        <x:v>1169</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>1185</x:v>
+        <x:v>1170</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="21.25" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
         <x:v>201</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>1188</x:v>
+        <x:v>1173</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22.899999618530273" customHeight="1">
       <x:c r="A3" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
         <x:v>268</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>1190</x:v>
+        <x:v>1175</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="23.75" customHeight="1">
       <x:c r="A4" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>289</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>1191</x:v>
+        <x:v>1176</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="23.899999618530273" customHeight="1">
       <x:c r="A5" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>310</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>1192</x:v>
+        <x:v>1177</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="21.25" customHeight="1">
       <x:c r="A6" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>409</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>1193</x:v>
+        <x:v>1178</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="23.75" customHeight="1">
       <x:c r="A7" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>445</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>1194</x:v>
+        <x:v>1179</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="23.899999618530273" customHeight="1">
       <x:c r="A8" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>1187</x:v>
-      </x:c>
-      <x:c r="C8" s="1" t="s">
-        <x:v>484</x:v>
+        <x:v>1172</x:v>
+      </x:c>
+      <x:c r="C8" s="1" t="str">
+        <x:v>WURKZ ORD</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>1195</x:v>
+        <x:v>1180</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="20.399999618530273" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C9" s="1" t="str">
         <x:v>CAMBODIA ED ORD</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>1196</x:v>
+        <x:v>1181</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="23.899999618530273" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C10" s="1" t="str">
         <x:v>DAZZ ORD</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>1197</x:v>
+        <x:v>1182</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="23.899999618530273" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C11" s="1" t="str">
         <x:v>DAZZ Zero Sugar ORD</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>1198</x:v>
+        <x:v>1183</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="23.899999618530273" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>645</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>1199</x:v>
+        <x:v>1184</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="23.899999618530273" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>690</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>1200</x:v>
+        <x:v>1185</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="23.899999618530273" customHeight="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C14" s="1" t="str">
         <x:v>EXPREZ Melon ORD</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>1201</x:v>
+        <x:v>1186</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="23.899999618530273" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C15" s="1" t="str">
         <x:v>Wurkz Ice ORD</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>1202</x:v>
+        <x:v>1187</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="23.899999618530273" customHeight="1">
@@ -20061,733 +20016,733 @@
     </x:row>
     <x:row r="17" ht="12.75" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C17" s="1" t="str">
         <x:v>CAMBODIA Sport 500mL ORD</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>1203</x:v>
+        <x:v>1188</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="12.75" customHeight="1">
       <x:c r="A18" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>810</x:v>
+        <x:v>795</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>1204</x:v>
+        <x:v>1189</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="12.75" customHeight="1">
       <x:c r="A19" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>881</x:v>
+        <x:v>866</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>1205</x:v>
+        <x:v>1190</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>1189</x:v>
+        <x:v>1174</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="12.75" customHeight="1">
       <x:c r="A20" s="1" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>1187</x:v>
+        <x:v>1172</x:v>
       </x:c>
       <x:c r="C20" s="1" t="str">
         <x:v>EXPREZ Can 330ml ORD</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>1206</x:v>
+        <x:v>1191</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>1207</x:v>
+        <x:v>1192</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="12.75" customHeight="1">
       <x:c r="A21" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>229</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>1210</x:v>
+        <x:v>1195</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="12.75" customHeight="1">
       <x:c r="A22" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>242</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>1212</x:v>
+        <x:v>1197</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="12.75" customHeight="1">
       <x:c r="A23" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>255</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>1213</x:v>
+        <x:v>1198</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="12.75" customHeight="1">
       <x:c r="A24" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>331</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>1214</x:v>
+        <x:v>1199</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="12.75" customHeight="1">
       <x:c r="A25" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>344</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>1215</x:v>
+        <x:v>1200</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="12.75" customHeight="1">
       <x:c r="A26" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>357</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>1216</x:v>
+        <x:v>1201</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="12.75" customHeight="1">
       <x:c r="A27" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>370</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>1217</x:v>
+        <x:v>1202</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="12.75" customHeight="1">
       <x:c r="A28" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
         <x:v>383</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>1218</x:v>
+        <x:v>1203</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="12.75" customHeight="1">
       <x:c r="A29" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>396</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>1219</x:v>
+        <x:v>1204</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="12.75" customHeight="1">
       <x:c r="A30" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>430</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>1220</x:v>
+        <x:v>1205</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="12.75" customHeight="1">
       <x:c r="A31" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>464</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>1221</x:v>
+        <x:v>1206</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="12.75" customHeight="1">
       <x:c r="A32" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C32" s="1" t="str">
         <x:v>Boostrong ORD</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>1222</x:v>
+        <x:v>1207</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="12.75" customHeight="1">
       <x:c r="A33" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C33" s="1" t="str">
         <x:v>Krud ED ORD</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>1223</x:v>
+        <x:v>1208</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="12.75" customHeight="1">
       <x:c r="A34" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C34" s="1" t="str">
         <x:v>Champion ORD</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>1224</x:v>
+        <x:v>1209</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="12.75" customHeight="1">
       <x:c r="A35" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C35" s="1" t="str">
         <x:v>King Kong Ice ORD</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>1225</x:v>
+        <x:v>1210</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="12.75" customHeight="1">
       <x:c r="A36" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C36" s="1" t="str">
         <x:v>Krud Ice ORD</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>1226</x:v>
+        <x:v>1211</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="12.75" customHeight="1">
       <x:c r="A37" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C37" s="1" t="str">
         <x:v>Super Boostrong ORD</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>1227</x:v>
+        <x:v>1212</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="12.75" customHeight="1">
       <x:c r="A38" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C38" s="1" t="str">
         <x:v>King Kong ORD</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>1228</x:v>
+        <x:v>1213</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="12.75" customHeight="1">
       <x:c r="A39" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>542</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>1229</x:v>
+        <x:v>1214</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="12.75" customHeight="1">
       <x:c r="A40" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>565</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>1230</x:v>
+        <x:v>1215</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="12.75" customHeight="1">
       <x:c r="A41" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>1209</x:v>
-      </x:c>
-      <x:c r="C41" s="1" t="s">
-        <x:v>578</x:v>
+        <x:v>1194</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="str">
+        <x:v>Dragon ORD</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>1231</x:v>
+        <x:v>1216</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="12.75" customHeight="1">
       <x:c r="A42" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>601</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>1232</x:v>
+        <x:v>1217</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="12.75" customHeight="1">
       <x:c r="A43" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>664</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>1233</x:v>
+        <x:v>1218</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="13.649999618530273" customHeight="1">
       <x:c r="A44" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>677</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>1234</x:v>
+        <x:v>1219</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="12.75" customHeight="1">
       <x:c r="A45" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>709</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>1235</x:v>
+        <x:v>1220</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="12.75" customHeight="1">
       <x:c r="A46" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>722</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>1236</x:v>
+        <x:v>1221</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="12.75" customHeight="1">
       <x:c r="A47" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>752</x:v>
+        <x:v>737</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>1237</x:v>
+        <x:v>1222</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="12.75" customHeight="1">
       <x:c r="A48" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C48" s="1" t="str">
         <x:v>Idol Can 330ml ORD</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>1238</x:v>
+        <x:v>1223</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="12.75" customHeight="1">
       <x:c r="A49" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>782</x:v>
+        <x:v>767</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>1239</x:v>
+        <x:v>1224</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="12.75" customHeight="1">
       <x:c r="A50" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>795</x:v>
+        <x:v>780</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>1240</x:v>
+        <x:v>1225</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="12.75" customHeight="1">
       <x:c r="A51" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>829</x:v>
+        <x:v>814</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>1241</x:v>
+        <x:v>1226</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="12.75" customHeight="1">
       <x:c r="A52" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>842</x:v>
+        <x:v>827</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>1242</x:v>
+        <x:v>1227</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="12.75" customHeight="1">
       <x:c r="A53" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>855</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>1243</x:v>
+        <x:v>1228</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="12.75" customHeight="1">
       <x:c r="A54" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>868</x:v>
+        <x:v>853</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>1244</x:v>
+        <x:v>1229</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>900</x:v>
+        <x:v>885</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>1245</x:v>
+        <x:v>1230</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="29">
       <x:c r="A56" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>913</x:v>
+        <x:v>898</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>1246</x:v>
+        <x:v>1231</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="29">
       <x:c r="A57" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>926</x:v>
+        <x:v>911</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>1247</x:v>
+        <x:v>1232</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="29">
       <x:c r="A58" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>1209</x:v>
+        <x:v>1194</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>939</x:v>
+        <x:v>924</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>1248</x:v>
+        <x:v>1233</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>1211</x:v>
+        <x:v>1196</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="1" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>1249</x:v>
+        <x:v>1234</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
         <x:v>289</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>1250</x:v>
+        <x:v>1235</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>1251</x:v>
+        <x:v>1236</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -20813,308 +20768,308 @@
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="1" t="s">
-        <x:v>1252</x:v>
+        <x:v>1237</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>1253</x:v>
+        <x:v>1238</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>1254</x:v>
+        <x:v>1239</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>956</x:v>
+        <x:v>941</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>1255</x:v>
+        <x:v>1240</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="1" t="s">
-        <x:v>1252</x:v>
+        <x:v>1237</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>1253</x:v>
+        <x:v>1238</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>961</x:v>
+        <x:v>946</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>960</x:v>
+        <x:v>945</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>1255</x:v>
+        <x:v>1240</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" t="s">
-        <x:v>1256</x:v>
+        <x:v>1241</x:v>
       </x:c>
       <x:c r="B65" t="s">
-        <x:v>1257</x:v>
+        <x:v>1242</x:v>
       </x:c>
       <x:c r="C65" t="s">
-        <x:v>1258</x:v>
+        <x:v>1243</x:v>
       </x:c>
       <x:c r="D65" t="s">
         <x:v>28</x:v>
       </x:c>
       <x:c r="E65" t="s">
-        <x:v>1259</x:v>
+        <x:v>1244</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" t="s">
-        <x:v>1256</x:v>
+        <x:v>1241</x:v>
       </x:c>
       <x:c r="B66" t="s">
-        <x:v>1152</x:v>
+        <x:v>1137</x:v>
       </x:c>
       <x:c r="C66" t="s">
-        <x:v>1117</x:v>
+        <x:v>1102</x:v>
       </x:c>
       <x:c r="D66" t="s">
-        <x:v>1260</x:v>
+        <x:v>1245</x:v>
       </x:c>
       <x:c r="E66" t="s">
-        <x:v>1261</x:v>
+        <x:v>1246</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B67" t="s">
-        <x:v>1262</x:v>
+        <x:v>1247</x:v>
       </x:c>
       <x:c r="C67" t="s">
         <x:v>92</x:v>
       </x:c>
       <x:c r="D67" t="s">
-        <x:v>1263</x:v>
+        <x:v>1248</x:v>
       </x:c>
       <x:c r="E67" t="s">
-        <x:v>1264</x:v>
+        <x:v>1249</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B68" t="s">
-        <x:v>1262</x:v>
+        <x:v>1247</x:v>
       </x:c>
       <x:c r="C68" t="s">
         <x:v>126</x:v>
       </x:c>
       <x:c r="D68" t="s">
-        <x:v>1265</x:v>
+        <x:v>1250</x:v>
       </x:c>
       <x:c r="E68" t="s">
-        <x:v>1264</x:v>
+        <x:v>1249</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B69" t="s">
-        <x:v>1262</x:v>
+        <x:v>1247</x:v>
       </x:c>
       <x:c r="C69" t="s">
         <x:v>137</x:v>
       </x:c>
       <x:c r="D69" t="s">
-        <x:v>1266</x:v>
+        <x:v>1251</x:v>
       </x:c>
       <x:c r="E69" t="s">
-        <x:v>1264</x:v>
+        <x:v>1249</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B70" t="s">
-        <x:v>1262</x:v>
+        <x:v>1247</x:v>
       </x:c>
       <x:c r="C70" t="s">
         <x:v>169</x:v>
       </x:c>
       <x:c r="D70" t="s">
-        <x:v>1267</x:v>
+        <x:v>1252</x:v>
       </x:c>
       <x:c r="E70" t="s">
-        <x:v>1264</x:v>
+        <x:v>1249</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B71" t="s">
-        <x:v>1268</x:v>
+        <x:v>1253</x:v>
       </x:c>
       <x:c r="C71" t="s">
         <x:v>112</x:v>
       </x:c>
       <x:c r="D71" t="s">
-        <x:v>1269</x:v>
+        <x:v>1254</x:v>
       </x:c>
       <x:c r="E71" t="s">
-        <x:v>1270</x:v>
+        <x:v>1255</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B72" t="s">
-        <x:v>1268</x:v>
+        <x:v>1253</x:v>
       </x:c>
       <x:c r="C72" t="s">
         <x:v>119</x:v>
       </x:c>
       <x:c r="D72" t="s">
-        <x:v>1271</x:v>
+        <x:v>1256</x:v>
       </x:c>
       <x:c r="E72" t="s">
-        <x:v>1270</x:v>
+        <x:v>1255</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B73" t="s">
-        <x:v>1268</x:v>
+        <x:v>1253</x:v>
       </x:c>
       <x:c r="C73" t="s">
         <x:v>148</x:v>
       </x:c>
       <x:c r="D73" t="s">
-        <x:v>1272</x:v>
+        <x:v>1257</x:v>
       </x:c>
       <x:c r="E73" t="s">
-        <x:v>1270</x:v>
+        <x:v>1255</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B74" t="s">
-        <x:v>1268</x:v>
+        <x:v>1253</x:v>
       </x:c>
       <x:c r="C74" t="s">
         <x:v>155</x:v>
       </x:c>
       <x:c r="D74" t="s">
-        <x:v>1273</x:v>
+        <x:v>1258</x:v>
       </x:c>
       <x:c r="E74" t="s">
-        <x:v>1270</x:v>
+        <x:v>1255</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B75" t="s">
-        <x:v>1268</x:v>
+        <x:v>1253</x:v>
       </x:c>
       <x:c r="C75" t="s">
         <x:v>162</x:v>
       </x:c>
       <x:c r="D75" t="s">
-        <x:v>1274</x:v>
+        <x:v>1259</x:v>
       </x:c>
       <x:c r="E75" t="s">
-        <x:v>1270</x:v>
+        <x:v>1255</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B76" t="s">
-        <x:v>1268</x:v>
+        <x:v>1253</x:v>
       </x:c>
       <x:c r="C76" t="s">
         <x:v>180</x:v>
       </x:c>
       <x:c r="D76" t="s">
-        <x:v>1275</x:v>
+        <x:v>1260</x:v>
       </x:c>
       <x:c r="E76" t="s">
-        <x:v>1270</x:v>
+        <x:v>1255</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B77" t="s">
-        <x:v>1268</x:v>
+        <x:v>1253</x:v>
       </x:c>
       <x:c r="C77" t="s">
         <x:v>187</x:v>
       </x:c>
       <x:c r="D77" t="s">
-        <x:v>1276</x:v>
+        <x:v>1261</x:v>
       </x:c>
       <x:c r="E77" t="s">
-        <x:v>1270</x:v>
+        <x:v>1255</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B78" t="s">
-        <x:v>1268</x:v>
+        <x:v>1253</x:v>
       </x:c>
       <x:c r="C78" t="s">
         <x:v>194</x:v>
       </x:c>
       <x:c r="D78" t="s">
-        <x:v>1277</x:v>
+        <x:v>1262</x:v>
       </x:c>
       <x:c r="E78" t="s">
-        <x:v>1270</x:v>
+        <x:v>1255</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" t="s">
-        <x:v>1208</x:v>
+        <x:v>1193</x:v>
       </x:c>
       <x:c r="B79" t="s">
-        <x:v>1268</x:v>
+        <x:v>1253</x:v>
       </x:c>
       <x:c r="C79" t="s">
         <x:v>477</x:v>
       </x:c>
       <x:c r="D79" t="s">
-        <x:v>1278</x:v>
+        <x:v>1263</x:v>
       </x:c>
       <x:c r="E79" t="s">
-        <x:v>1270</x:v>
+        <x:v>1255</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" t="s">
-        <x:v>1186</x:v>
+        <x:v>1171</x:v>
       </x:c>
       <x:c r="B80" t="s">
-        <x:v>1262</x:v>
+        <x:v>1247</x:v>
       </x:c>
       <x:c r="C80" t="str">
         <x:v>EXPREZ Melon ORD</x:v>
       </x:c>
       <x:c r="D80" t="s">
-        <x:v>1279</x:v>
+        <x:v>1264</x:v>
       </x:c>
       <x:c r="E80" t="s">
-        <x:v>1280</x:v>
+        <x:v>1265</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
